--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$W$1:$W$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AH$1:$AH$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DU$1:$DU$4</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="918">
   <si>
     <t>alias</t>
   </si>
@@ -453,6 +453,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -543,6 +546,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1026,7 +1032,7 @@
     <t>sample transport conditions</t>
   </si>
   <si>
-    <t>(Optional) Sample transport duration (in days or hrs) and temperature the sample was exposed to (e.g. 5.5 days; 20 °c) (Units: m2)</t>
+    <t>(Optional) Sample transport duration (in days or hrs) and temperature the sample was exposed to (e.g. 5.5 days; 20 °c) (Units: ha)</t>
   </si>
   <si>
     <t>sample collection device</t>
@@ -1062,7 +1068,7 @@
     <t>sample measured depth</t>
   </si>
   <si>
-    <t>(Optional) In non deviated well, measured depth is equal to the true vertical depth, tvd (tvd=tvdss plus the reference or datum it refers to). in deviated wells, the md is the length of trajectory of the borehole measured from the same reference or datum. common datums used are ground level (gl), drilling rig floor (df), rotary table (rt), kelly bushing (kb) and mean sea level (msl). if "other" is specified, please propose entry in "additional info" field (Units: mm)</t>
+    <t>(Optional) In non deviated well, measured depth is equal to the true vertical depth, tvd (tvd=tvdss plus the reference or datum it refers to). in deviated wells, the md is the length of trajectory of the borehole measured from the same reference or datum. common datums used are ground level (gl), drilling rig floor (df), rotary table (rt), kelly bushing (kb) and mean sea level (msl). if "other" is specified, please propose entry in "additional info" field (Units: m)</t>
   </si>
   <si>
     <t>corrosion rate at sample location</t>
@@ -1203,13 +1209,13 @@
     <t>well identification number</t>
   </si>
   <si>
-    <t>(Optional) A unique identifier of a well or wellbore. this is part of the global framework for well identification initiative which is compiled by the professional petroleum data management association (ppdm) in an effort to improve well identification systems. (supporting information: https://ppdm.org/ and http://dl.ppdm.org/dl/690) (Units: year)</t>
+    <t>(Optional) A unique identifier of a well or wellbore. this is part of the global framework for well identification initiative which is compiled by the professional petroleum data management association (ppdm) in an effort to improve well identification systems. (supporting information: https://ppdm.org/ and http://dl.ppdm.org/dl/690) (Units: minute)</t>
   </si>
   <si>
     <t>water cut</t>
   </si>
   <si>
-    <t>(Optional) Current amount of water (%) in a produced fluid stream; or the average of the combined streams (Units: year)</t>
+    <t>(Optional) Current amount of water (%) in a produced fluid stream; or the average of the combined streams (Units: minute)</t>
   </si>
   <si>
     <t>production rate</t>
@@ -1287,7 +1293,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -1305,7 +1311,7 @@
     <t>hydrocarbon type produced</t>
   </si>
   <si>
-    <t>(Optional) Main hydrocarbon type produced from resource (i.e. oil, gas, condensate, etc). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Main hydrocarbon type produced from resource (i.e. oil, gas, condensate, etc). if "other" is specified, please propose entry in "additional info" field (Units: minute)</t>
   </si>
   <si>
     <t>api gravity</t>
@@ -1533,9 +1539,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1554,6 +1557,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1755,6 +1761,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1764,9 +1773,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1806,7 +1812,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1875,6 +1881,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1950,6 +1959,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1971,6 +1983,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2016,6 +2031,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2028,6 +2046,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2037,9 +2058,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2064,6 +2082,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2124,12 +2145,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2208,7 +2229,7 @@
     <t>pressure</t>
   </si>
   <si>
-    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: bar)</t>
+    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: atm)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2232,7 +2253,7 @@
     <t>permeability</t>
   </si>
   <si>
-    <t>(Optional) Measure of the ability of a hydrocarbon resource to allow fluids to pass through it. (additional information: https://en.wikipedia.org/wiki/permeability_(earth_sciences)) (Units: mm)</t>
+    <t>(Optional) Measure of the ability of a hydrocarbon resource to allow fluids to pass through it. (additional information: https://en.wikipedia.org/wiki/permeability_(earth_sciences)) (Units: m)</t>
   </si>
   <si>
     <t>oil water contact depth</t>
@@ -2244,7 +2265,7 @@
     <t>hydrocarbon resource original pressure</t>
   </si>
   <si>
-    <t>(Optional) Original pressure of the hydrocarbon resource (Units: Pa)</t>
+    <t>(Optional) Original pressure of the hydrocarbon resource (Units: N/m2)</t>
   </si>
   <si>
     <t>source rock geological age</t>
@@ -2268,7 +2289,7 @@
     <t>calcium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of calcium (Units: µmol/L)</t>
+    <t>(Optional) Concentration of calcium (Units: mg/L)</t>
   </si>
   <si>
     <t>chloride</t>
@@ -2280,7 +2301,7 @@
     <t>suspended solids</t>
   </si>
   <si>
-    <t>(Optional) Concentration of substances including a wide variety of material, such as silt, decaying plant and animal matter, etc,; can include multiple substances (Units: parts/million)</t>
+    <t>(Optional) Concentration of substances including a wide variety of material, such as silt, decaying plant and animal matter, etc,; can include multiple substances (Units: g/L)</t>
   </si>
   <si>
     <t>dissolved carbon dioxide</t>
@@ -2310,7 +2331,7 @@
     <t>magnesium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of magnesium (Units: parts/million)</t>
+    <t>(Optional) Concentration of magnesium (Units: mg/L)</t>
   </si>
   <si>
     <t>nitrate</t>
@@ -2352,13 +2373,13 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfate (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfate (Units: mg/L)</t>
   </si>
   <si>
     <t>sulfide</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfide (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfide (Units: mg/L)</t>
   </si>
   <si>
     <t>total phosphorus</t>
@@ -2394,13 +2415,13 @@
     <t>dissolved oxygen in fluids</t>
   </si>
   <si>
-    <t>(Optional) Concentration of dissolved oxygen in the oil field produced fluids as it contributes to oxgyen-corrosion and microbial activity (e.g. mic). (Units: µmol/kg)</t>
+    <t>(Optional) Concentration of dissolved oxygen in the oil field produced fluids as it contributes to oxgyen-corrosion and microbial activity (e.g. mic). (Units: µg/L)</t>
   </si>
   <si>
     <t>total sulfur</t>
   </si>
   <si>
-    <t>(Optional) Concentration of total sulfur in the sample (Units: µmol/L)</t>
+    <t>(Optional) Concentration of total sulfur in the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>injection water fraction</t>
@@ -2412,7 +2433,7 @@
     <t>ethylbenzene</t>
   </si>
   <si>
-    <t>(Optional) Concentration of ethylbenzene in the sample (Units: µmol/L)</t>
+    <t>(Optional) Concentration of ethylbenzene in the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>vfa in formation water</t>
@@ -2430,13 +2451,13 @@
     <t>sulfate in formation water</t>
   </si>
   <si>
-    <t>(Optional) Original sulfate concentration in the hydrocarbon resource (Units: year)</t>
+    <t>(Optional) Original sulfate concentration in the hydrocarbon resource (Units: minute)</t>
   </si>
   <si>
     <t>toluene</t>
   </si>
   <si>
-    <t>(Optional) Concentration of toluene in the sample (Units: year)</t>
+    <t>(Optional) Concentration of toluene in the sample (Units: minute)</t>
   </si>
   <si>
     <t>asphaltenes wt%</t>
@@ -2478,7 +2499,7 @@
     <t>source rock lithology</t>
   </si>
   <si>
-    <t>(Optional) Lithology of source rock (https://en.wikipedia.org/wiki/source_rock). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Lithology of source rock (https://en.wikipedia.org/wiki/source_rock). if "other" is specified, please propose entry in "additional info" field (Units: minute)</t>
   </si>
   <si>
     <t>sample material type</t>
@@ -2508,7 +2529,7 @@
     <t>biocide administration</t>
   </si>
   <si>
-    <t>(Optional) List of biocides (commercial name of product and supplier) and date of administration (Units: year)</t>
+    <t>(Optional) List of biocides (commercial name of product and supplier) and date of administration (Units: minute)</t>
   </si>
   <si>
     <t>chemical treatment method</t>
@@ -2616,7 +2637,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2703,7 +2724,7 @@
     <t>basin name</t>
   </si>
   <si>
-    <t>(Optional) Name of the basin (e.g. campos) (Units: g/m3)</t>
+    <t>(Optional) Name of the basin (e.g. campos) (Units: %)</t>
   </si>
   <si>
     <t>pour point</t>
@@ -2751,7 +2772,7 @@
     <t>lithology</t>
   </si>
   <si>
-    <t>(Optional) Hydrocarbon resource main lithology (additional information: http://petrowiki.org/lithology_and_rock_type_determination). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Hydrocarbon resource main lithology (additional information: http://petrowiki.org/lithology_and_rock_type_determination). if "other" is specified, please propose entry in "additional info" field (Units: minute)</t>
   </si>
   <si>
     <t>hydrocarbon resource original temperature</t>
@@ -2763,7 +2784,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>injection water breakthrough date of specific well</t>
@@ -3296,10 +3317,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3340,10 +3361,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3370,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3387,7 +3408,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3404,7 +3425,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3421,7 +3442,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3438,7 +3459,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3455,7 +3476,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3472,7 +3493,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3489,7 +3510,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3506,7 +3527,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3523,7 +3544,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3537,7 +3558,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3551,7 +3572,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3565,7 +3586,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3579,7 +3600,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3593,7 +3614,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3607,7 +3628,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3621,7 +3642,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3635,7 +3656,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3645,8 +3666,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3657,7 +3681,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3668,7 +3692,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3679,7 +3703,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3690,7 +3714,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3701,7 +3725,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3712,7 +3736,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3723,7 +3747,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3734,7 +3758,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3745,7 +3769,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3756,7 +3780,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3767,7 +3791,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3778,7 +3802,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3789,7 +3813,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3797,7 +3821,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3805,7 +3829,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3813,7 +3837,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3821,7 +3845,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3829,7 +3853,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3837,7 +3861,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3845,7 +3869,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3853,7 +3877,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3861,7 +3885,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3869,236 +3893,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4120,27 +4149,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4160,122 +4189,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4299,924 +4328,924 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:154" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -5252,1611 +5281,1636 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:DU289"/>
+  <dimension ref="H1:DU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:125">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AH1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BG1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="DU1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
     </row>
     <row r="2" spans="8:125">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="W2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AH2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BG2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="DU2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="3" spans="8:125">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AH3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="BG3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="DU3" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" spans="8:125">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BG4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DU4" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="8:125">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BG5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="8:125">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BG6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="8:125">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BG7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="8:125">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BG8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="8:125">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BG9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="8:125">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="BG10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="8:125">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="BG11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="8:125">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="BG12" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="8:125">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="BG13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="8:125">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="BG14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="8:125">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="BG15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="8:125">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="BG16" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="8:59">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="BG17" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" spans="8:59">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="BG18" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="8:59">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="BG19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="8:59">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="BG20" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="8:59">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="BG21" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="8:59">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="BG22" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="8:59">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="BG23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="8:59">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="BG24" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="8:59">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="BG25" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="8:59">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="BG26" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="8:59">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BG27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="8:59">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="BG28" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="8:59">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="BG29" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" spans="8:59">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="BG30" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="8:59">
       <c r="BG31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="32" spans="8:59">
       <c r="BG32" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="59:59">
       <c r="BG33" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34" spans="59:59">
       <c r="BG34" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35" spans="59:59">
       <c r="BG35" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="59:59">
       <c r="BG36" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="59:59">
       <c r="BG37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="59:59">
       <c r="BG38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" spans="59:59">
       <c r="BG39" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="59:59">
       <c r="BG40" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="59:59">
       <c r="BG41" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="42" spans="59:59">
       <c r="BG42" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="59:59">
       <c r="BG43" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="59:59">
       <c r="BG44" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" spans="59:59">
       <c r="BG45" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="59:59">
       <c r="BG46" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="59:59">
       <c r="BG47" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="59:59">
       <c r="BG48" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="59:59">
       <c r="BG49" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" spans="59:59">
       <c r="BG50" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51" spans="59:59">
       <c r="BG51" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" spans="59:59">
       <c r="BG52" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="59:59">
       <c r="BG53" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="54" spans="59:59">
       <c r="BG54" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="59:59">
       <c r="BG55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="59:59">
       <c r="BG56" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" spans="59:59">
       <c r="BG57" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="59:59">
       <c r="BG58" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="59" spans="59:59">
       <c r="BG59" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="60" spans="59:59">
       <c r="BG60" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" spans="59:59">
       <c r="BG61" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="62" spans="59:59">
       <c r="BG62" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="63" spans="59:59">
       <c r="BG63" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" spans="59:59">
       <c r="BG64" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="65" spans="59:59">
       <c r="BG65" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="66" spans="59:59">
       <c r="BG66" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="59:59">
       <c r="BG67" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="68" spans="59:59">
       <c r="BG68" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="59:59">
       <c r="BG69" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="59:59">
       <c r="BG70" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="59:59">
       <c r="BG71" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="59:59">
       <c r="BG72" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="59:59">
       <c r="BG73" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="59:59">
       <c r="BG74" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="59:59">
       <c r="BG75" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="59:59">
       <c r="BG76" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="59:59">
       <c r="BG77" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="59:59">
       <c r="BG78" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="79" spans="59:59">
       <c r="BG79" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="80" spans="59:59">
       <c r="BG80" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="81" spans="59:59">
       <c r="BG81" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="82" spans="59:59">
       <c r="BG82" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="83" spans="59:59">
       <c r="BG83" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" spans="59:59">
       <c r="BG84" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="85" spans="59:59">
       <c r="BG85" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="86" spans="59:59">
       <c r="BG86" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="87" spans="59:59">
       <c r="BG87" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="88" spans="59:59">
       <c r="BG88" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="89" spans="59:59">
       <c r="BG89" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" spans="59:59">
       <c r="BG90" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" spans="59:59">
       <c r="BG91" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="92" spans="59:59">
       <c r="BG92" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="93" spans="59:59">
       <c r="BG93" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="94" spans="59:59">
       <c r="BG94" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="95" spans="59:59">
       <c r="BG95" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="96" spans="59:59">
       <c r="BG96" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="97" spans="59:59">
       <c r="BG97" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="98" spans="59:59">
       <c r="BG98" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="99" spans="59:59">
       <c r="BG99" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100" spans="59:59">
       <c r="BG100" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="101" spans="59:59">
       <c r="BG101" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="102" spans="59:59">
       <c r="BG102" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="103" spans="59:59">
       <c r="BG103" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="104" spans="59:59">
       <c r="BG104" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="105" spans="59:59">
       <c r="BG105" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="106" spans="59:59">
       <c r="BG106" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="107" spans="59:59">
       <c r="BG107" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="108" spans="59:59">
       <c r="BG108" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="109" spans="59:59">
       <c r="BG109" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="110" spans="59:59">
       <c r="BG110" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="111" spans="59:59">
       <c r="BG111" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="112" spans="59:59">
       <c r="BG112" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113" spans="59:59">
       <c r="BG113" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" spans="59:59">
       <c r="BG114" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="115" spans="59:59">
       <c r="BG115" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="116" spans="59:59">
       <c r="BG116" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="117" spans="59:59">
       <c r="BG117" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="59:59">
       <c r="BG118" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="119" spans="59:59">
       <c r="BG119" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="120" spans="59:59">
       <c r="BG120" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="121" spans="59:59">
       <c r="BG121" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="59:59">
       <c r="BG122" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="123" spans="59:59">
       <c r="BG123" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124" spans="59:59">
       <c r="BG124" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="125" spans="59:59">
       <c r="BG125" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126" spans="59:59">
       <c r="BG126" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="127" spans="59:59">
       <c r="BG127" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="59:59">
       <c r="BG128" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="129" spans="59:59">
       <c r="BG129" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="130" spans="59:59">
       <c r="BG130" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="131" spans="59:59">
       <c r="BG131" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="132" spans="59:59">
       <c r="BG132" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="133" spans="59:59">
       <c r="BG133" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="134" spans="59:59">
       <c r="BG134" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135" spans="59:59">
       <c r="BG135" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="136" spans="59:59">
       <c r="BG136" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="137" spans="59:59">
       <c r="BG137" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="138" spans="59:59">
       <c r="BG138" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="139" spans="59:59">
       <c r="BG139" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="140" spans="59:59">
       <c r="BG140" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="141" spans="59:59">
       <c r="BG141" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="142" spans="59:59">
       <c r="BG142" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="143" spans="59:59">
       <c r="BG143" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="144" spans="59:59">
       <c r="BG144" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="145" spans="59:59">
       <c r="BG145" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="146" spans="59:59">
       <c r="BG146" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="147" spans="59:59">
       <c r="BG147" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="148" spans="59:59">
       <c r="BG148" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="149" spans="59:59">
       <c r="BG149" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="150" spans="59:59">
       <c r="BG150" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="151" spans="59:59">
       <c r="BG151" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="152" spans="59:59">
       <c r="BG152" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="59:59">
       <c r="BG153" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="154" spans="59:59">
       <c r="BG154" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="155" spans="59:59">
       <c r="BG155" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="156" spans="59:59">
       <c r="BG156" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="157" spans="59:59">
       <c r="BG157" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="158" spans="59:59">
       <c r="BG158" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="59:59">
       <c r="BG159" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="160" spans="59:59">
       <c r="BG160" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="161" spans="59:59">
       <c r="BG161" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="162" spans="59:59">
       <c r="BG162" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="163" spans="59:59">
       <c r="BG163" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="164" spans="59:59">
       <c r="BG164" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="165" spans="59:59">
       <c r="BG165" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="166" spans="59:59">
       <c r="BG166" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="167" spans="59:59">
       <c r="BG167" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="168" spans="59:59">
       <c r="BG168" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="169" spans="59:59">
       <c r="BG169" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="170" spans="59:59">
       <c r="BG170" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="171" spans="59:59">
       <c r="BG171" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="172" spans="59:59">
       <c r="BG172" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" spans="59:59">
       <c r="BG173" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" spans="59:59">
       <c r="BG174" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="175" spans="59:59">
       <c r="BG175" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="176" spans="59:59">
       <c r="BG176" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="177" spans="59:59">
       <c r="BG177" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="178" spans="59:59">
       <c r="BG178" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="179" spans="59:59">
       <c r="BG179" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="180" spans="59:59">
       <c r="BG180" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="181" spans="59:59">
       <c r="BG181" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="182" spans="59:59">
       <c r="BG182" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="183" spans="59:59">
       <c r="BG183" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="184" spans="59:59">
       <c r="BG184" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="185" spans="59:59">
       <c r="BG185" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="186" spans="59:59">
       <c r="BG186" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="59:59">
       <c r="BG187" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="188" spans="59:59">
       <c r="BG188" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="189" spans="59:59">
       <c r="BG189" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="190" spans="59:59">
       <c r="BG190" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="191" spans="59:59">
       <c r="BG191" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="192" spans="59:59">
       <c r="BG192" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="193" spans="59:59">
       <c r="BG193" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="194" spans="59:59">
       <c r="BG194" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="195" spans="59:59">
       <c r="BG195" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="196" spans="59:59">
       <c r="BG196" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="197" spans="59:59">
       <c r="BG197" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="198" spans="59:59">
       <c r="BG198" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="199" spans="59:59">
       <c r="BG199" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="200" spans="59:59">
       <c r="BG200" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="201" spans="59:59">
       <c r="BG201" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="202" spans="59:59">
       <c r="BG202" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="203" spans="59:59">
       <c r="BG203" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="204" spans="59:59">
       <c r="BG204" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="205" spans="59:59">
       <c r="BG205" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="206" spans="59:59">
       <c r="BG206" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="207" spans="59:59">
       <c r="BG207" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="208" spans="59:59">
       <c r="BG208" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="209" spans="59:59">
       <c r="BG209" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="210" spans="59:59">
       <c r="BG210" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="211" spans="59:59">
       <c r="BG211" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="212" spans="59:59">
       <c r="BG212" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="213" spans="59:59">
       <c r="BG213" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="214" spans="59:59">
       <c r="BG214" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="215" spans="59:59">
       <c r="BG215" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="216" spans="59:59">
       <c r="BG216" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="217" spans="59:59">
       <c r="BG217" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218" spans="59:59">
       <c r="BG218" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="219" spans="59:59">
       <c r="BG219" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="220" spans="59:59">
       <c r="BG220" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="221" spans="59:59">
       <c r="BG221" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="222" spans="59:59">
       <c r="BG222" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="223" spans="59:59">
       <c r="BG223" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="224" spans="59:59">
       <c r="BG224" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="225" spans="59:59">
       <c r="BG225" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="226" spans="59:59">
       <c r="BG226" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="227" spans="59:59">
       <c r="BG227" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="228" spans="59:59">
       <c r="BG228" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="229" spans="59:59">
       <c r="BG229" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="230" spans="59:59">
       <c r="BG230" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="231" spans="59:59">
       <c r="BG231" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="232" spans="59:59">
       <c r="BG232" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="233" spans="59:59">
       <c r="BG233" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="234" spans="59:59">
       <c r="BG234" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="235" spans="59:59">
       <c r="BG235" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="236" spans="59:59">
       <c r="BG236" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="237" spans="59:59">
       <c r="BG237" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="238" spans="59:59">
       <c r="BG238" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="239" spans="59:59">
       <c r="BG239" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="240" spans="59:59">
       <c r="BG240" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="241" spans="59:59">
       <c r="BG241" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="242" spans="59:59">
       <c r="BG242" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="243" spans="59:59">
       <c r="BG243" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="244" spans="59:59">
       <c r="BG244" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="245" spans="59:59">
       <c r="BG245" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="246" spans="59:59">
       <c r="BG246" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="247" spans="59:59">
       <c r="BG247" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="248" spans="59:59">
       <c r="BG248" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="249" spans="59:59">
       <c r="BG249" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="250" spans="59:59">
       <c r="BG250" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="251" spans="59:59">
       <c r="BG251" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="252" spans="59:59">
       <c r="BG252" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="253" spans="59:59">
       <c r="BG253" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="254" spans="59:59">
       <c r="BG254" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="255" spans="59:59">
       <c r="BG255" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="256" spans="59:59">
       <c r="BG256" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="257" spans="59:59">
       <c r="BG257" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="258" spans="59:59">
       <c r="BG258" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="259" spans="59:59">
       <c r="BG259" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="260" spans="59:59">
       <c r="BG260" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="261" spans="59:59">
       <c r="BG261" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="262" spans="59:59">
       <c r="BG262" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="263" spans="59:59">
       <c r="BG263" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="264" spans="59:59">
       <c r="BG264" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="265" spans="59:59">
       <c r="BG265" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="266" spans="59:59">
       <c r="BG266" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="267" spans="59:59">
       <c r="BG267" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="268" spans="59:59">
       <c r="BG268" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="269" spans="59:59">
       <c r="BG269" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="270" spans="59:59">
       <c r="BG270" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="271" spans="59:59">
       <c r="BG271" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="272" spans="59:59">
       <c r="BG272" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="273" spans="59:59">
       <c r="BG273" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="274" spans="59:59">
       <c r="BG274" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="275" spans="59:59">
       <c r="BG275" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="276" spans="59:59">
       <c r="BG276" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="277" spans="59:59">
       <c r="BG277" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="278" spans="59:59">
       <c r="BG278" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="279" spans="59:59">
       <c r="BG279" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="280" spans="59:59">
       <c r="BG280" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="281" spans="59:59">
       <c r="BG281" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="282" spans="59:59">
       <c r="BG282" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="283" spans="59:59">
       <c r="BG283" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="284" spans="59:59">
       <c r="BG284" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="285" spans="59:59">
       <c r="BG285" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="286" spans="59:59">
       <c r="BG286" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="287" spans="59:59">
       <c r="BG287" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="288" spans="59:59">
       <c r="BG288" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="289" spans="59:59">
       <c r="BG289" t="s">
-        <v>715</v>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="290" spans="59:59">
+      <c r="BG290" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="291" spans="59:59">
+      <c r="BG291" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="292" spans="59:59">
+      <c r="BG292" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="293" spans="59:59">
+      <c r="BG293" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="294" spans="59:59">
+      <c r="BG294" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -18,26 +18,26 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BE$1:$BE$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BF$1:$BF$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$U$1:$U$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AF$1:$AF$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DS$1:$DS$4</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$V$1:$V$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AG$1:$AG$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DT$1:$DT$4</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="916">
   <si>
     <t>alias</t>
   </si>
@@ -453,6 +453,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -543,6 +546,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -843,6 +849,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1521,9 +1533,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1542,6 +1551,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1743,6 +1755,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1752,9 +1767,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1794,7 +1806,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1863,6 +1875,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1938,6 +1953,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1959,6 +1977,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2004,6 +2025,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2016,6 +2040,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2025,9 +2052,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2052,6 +2076,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2112,10 +2139,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3284,10 +3311,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3328,10 +3355,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3358,7 +3385,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3375,7 +3402,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3392,7 +3419,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3409,7 +3436,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3426,7 +3453,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3443,7 +3470,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3460,7 +3487,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3477,7 +3504,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3494,7 +3521,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3511,7 +3538,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3525,7 +3552,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3539,7 +3566,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3553,7 +3580,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3567,7 +3594,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3581,7 +3608,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3595,7 +3622,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3609,7 +3636,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3623,7 +3650,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3633,8 +3660,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3645,7 +3675,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3656,7 +3686,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3667,7 +3697,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3678,7 +3708,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3689,7 +3719,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3700,7 +3730,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3711,7 +3741,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3722,7 +3752,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3733,7 +3763,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3744,7 +3774,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3755,7 +3785,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3766,7 +3796,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3777,7 +3807,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3785,7 +3815,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3793,7 +3823,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3801,7 +3831,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3809,7 +3839,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3817,7 +3847,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3825,7 +3855,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3833,7 +3863,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3841,7 +3871,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3849,7 +3879,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3857,236 +3887,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4108,27 +4143,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4148,122 +4183,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4273,13 +4308,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EV2"/>
+  <dimension ref="A1:EW2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:152">
+    <row r="1" spans="1:153">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4287,938 +4322,944 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>712</v>
+        <v>425</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="2" spans="1:152" ht="150" customHeight="1">
+        <v>912</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:153" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>713</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>797</v>
+        <v>884</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>878</v>
+        <v>806</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
+      </c>
+      <c r="EW2" s="2" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3:AG101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ3:AJ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK3:AK101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE3:BE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DS3:DS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DT3:DT101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -5228,1611 +5269,1636 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:DS289"/>
+  <dimension ref="G1:DT294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:123">
-      <c r="F1" t="s">
-        <v>272</v>
-      </c>
+    <row r="1" spans="7:124">
       <c r="G1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="V1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>372</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>383</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>427</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="2" spans="7:124">
+      <c r="G2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" t="s">
+        <v>318</v>
+      </c>
+      <c r="V2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>373</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>428</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="7:124">
+      <c r="G3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J3" t="s">
+        <v>319</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>374</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>429</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="4" spans="7:124">
+      <c r="G4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" t="s">
+        <v>320</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>430</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="5" spans="7:124">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="7:124">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J6" t="s">
+        <v>322</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="7" spans="7:124">
+      <c r="G7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" spans="7:124">
+      <c r="G8" t="s">
+        <v>283</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="7:124">
+      <c r="G9" t="s">
+        <v>284</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="7:124">
+      <c r="G10" t="s">
+        <v>285</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="7:124">
+      <c r="G11" t="s">
+        <v>286</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="12" spans="7:124">
+      <c r="G12" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="7:124">
+      <c r="G13" t="s">
+        <v>288</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" spans="7:124">
+      <c r="G14" t="s">
+        <v>289</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="7:124">
+      <c r="G15" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="16" spans="7:124">
+      <c r="G16" t="s">
+        <v>291</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="17" spans="7:58">
+      <c r="G17" t="s">
+        <v>292</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="7:58">
+      <c r="G18" t="s">
+        <v>293</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="7:58">
+      <c r="G19" t="s">
+        <v>294</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="20" spans="7:58">
+      <c r="G20" t="s">
+        <v>295</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="7:58">
+      <c r="G21" t="s">
+        <v>296</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="22" spans="7:58">
+      <c r="G22" t="s">
+        <v>297</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="23" spans="7:58">
+      <c r="G23" t="s">
+        <v>298</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="24" spans="7:58">
+      <c r="G24" t="s">
+        <v>299</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="7:58">
+      <c r="G25" t="s">
+        <v>300</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="26" spans="7:58">
+      <c r="G26" t="s">
+        <v>301</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="27" spans="7:58">
+      <c r="G27" t="s">
+        <v>302</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="28" spans="7:58">
+      <c r="G28" t="s">
+        <v>303</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="29" spans="7:58">
+      <c r="G29" t="s">
         <v>304</v>
       </c>
-      <c r="I1" t="s">
-        <v>313</v>
-      </c>
-      <c r="U1" t="s">
-        <v>344</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>368</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>379</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>423</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="2" spans="6:123">
-      <c r="F2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="BF29" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="30" spans="7:58">
+      <c r="G30" t="s">
         <v>305</v>
       </c>
-      <c r="I2" t="s">
-        <v>314</v>
-      </c>
-      <c r="U2" t="s">
-        <v>345</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>380</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>424</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="3" spans="6:123">
-      <c r="F3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I3" t="s">
-        <v>315</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>370</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>425</v>
-      </c>
-      <c r="DS3" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="4" spans="6:123">
-      <c r="F4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I4" t="s">
-        <v>316</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>426</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="5" spans="6:123">
-      <c r="F5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G5" t="s">
-        <v>308</v>
-      </c>
-      <c r="I5" t="s">
-        <v>317</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="6" spans="6:123">
-      <c r="F6" t="s">
-        <v>277</v>
-      </c>
-      <c r="I6" t="s">
-        <v>318</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="7" spans="6:123">
-      <c r="F7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I7" t="s">
-        <v>319</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="8" spans="6:123">
-      <c r="F8" t="s">
-        <v>279</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="9" spans="6:123">
-      <c r="F9" t="s">
-        <v>280</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="10" spans="6:123">
-      <c r="F10" t="s">
-        <v>281</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="11" spans="6:123">
-      <c r="F11" t="s">
-        <v>282</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="12" spans="6:123">
-      <c r="F12" t="s">
-        <v>283</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="13" spans="6:123">
-      <c r="F13" t="s">
-        <v>284</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="14" spans="6:123">
-      <c r="F14" t="s">
-        <v>285</v>
-      </c>
-      <c r="BE14" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="15" spans="6:123">
-      <c r="F15" t="s">
-        <v>286</v>
-      </c>
-      <c r="BE15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="16" spans="6:123">
-      <c r="F16" t="s">
-        <v>287</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="17" spans="6:57">
-      <c r="F17" t="s">
-        <v>288</v>
-      </c>
-      <c r="BE17" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="18" spans="6:57">
-      <c r="F18" t="s">
-        <v>289</v>
-      </c>
-      <c r="BE18" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="19" spans="6:57">
-      <c r="F19" t="s">
-        <v>290</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="20" spans="6:57">
-      <c r="F20" t="s">
-        <v>291</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="21" spans="6:57">
-      <c r="F21" t="s">
-        <v>292</v>
-      </c>
-      <c r="BE21" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="22" spans="6:57">
-      <c r="F22" t="s">
-        <v>293</v>
-      </c>
-      <c r="BE22" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="23" spans="6:57">
-      <c r="F23" t="s">
-        <v>294</v>
-      </c>
-      <c r="BE23" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="24" spans="6:57">
-      <c r="F24" t="s">
-        <v>295</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="25" spans="6:57">
-      <c r="F25" t="s">
-        <v>296</v>
-      </c>
-      <c r="BE25" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="26" spans="6:57">
-      <c r="F26" t="s">
-        <v>297</v>
-      </c>
-      <c r="BE26" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="27" spans="6:57">
-      <c r="F27" t="s">
-        <v>298</v>
-      </c>
-      <c r="BE27" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="28" spans="6:57">
-      <c r="F28" t="s">
-        <v>299</v>
-      </c>
-      <c r="BE28" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="29" spans="6:57">
-      <c r="F29" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE29" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="30" spans="6:57">
-      <c r="F30" t="s">
-        <v>301</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="31" spans="6:57">
-      <c r="BE31" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="32" spans="6:57">
-      <c r="BE32" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="33" spans="57:57">
-      <c r="BE33" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="34" spans="57:57">
-      <c r="BE34" t="s">
+      <c r="BF30" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="35" spans="57:57">
-      <c r="BE35" t="s">
+    <row r="31" spans="7:58">
+      <c r="BF31" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="36" spans="57:57">
-      <c r="BE36" t="s">
+    <row r="32" spans="7:58">
+      <c r="BF32" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="37" spans="57:57">
-      <c r="BE37" t="s">
+    <row r="33" spans="58:58">
+      <c r="BF33" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="57:57">
-      <c r="BE38" t="s">
+    <row r="34" spans="58:58">
+      <c r="BF34" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="39" spans="57:57">
-      <c r="BE39" t="s">
+    <row r="35" spans="58:58">
+      <c r="BF35" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="40" spans="57:57">
-      <c r="BE40" t="s">
+    <row r="36" spans="58:58">
+      <c r="BF36" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="57:57">
-      <c r="BE41" t="s">
+    <row r="37" spans="58:58">
+      <c r="BF37" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="42" spans="57:57">
-      <c r="BE42" t="s">
+    <row r="38" spans="58:58">
+      <c r="BF38" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="43" spans="57:57">
-      <c r="BE43" t="s">
+    <row r="39" spans="58:58">
+      <c r="BF39" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="44" spans="57:57">
-      <c r="BE44" t="s">
+    <row r="40" spans="58:58">
+      <c r="BF40" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="45" spans="57:57">
-      <c r="BE45" t="s">
+    <row r="41" spans="58:58">
+      <c r="BF41" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="46" spans="57:57">
-      <c r="BE46" t="s">
+    <row r="42" spans="58:58">
+      <c r="BF42" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="47" spans="57:57">
-      <c r="BE47" t="s">
+    <row r="43" spans="58:58">
+      <c r="BF43" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="48" spans="57:57">
-      <c r="BE48" t="s">
+    <row r="44" spans="58:58">
+      <c r="BF44" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="49" spans="57:57">
-      <c r="BE49" t="s">
+    <row r="45" spans="58:58">
+      <c r="BF45" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="50" spans="57:57">
-      <c r="BE50" t="s">
+    <row r="46" spans="58:58">
+      <c r="BF46" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="51" spans="57:57">
-      <c r="BE51" t="s">
+    <row r="47" spans="58:58">
+      <c r="BF47" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="52" spans="57:57">
-      <c r="BE52" t="s">
+    <row r="48" spans="58:58">
+      <c r="BF48" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="53" spans="57:57">
-      <c r="BE53" t="s">
+    <row r="49" spans="58:58">
+      <c r="BF49" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="54" spans="57:57">
-      <c r="BE54" t="s">
+    <row r="50" spans="58:58">
+      <c r="BF50" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="55" spans="57:57">
-      <c r="BE55" t="s">
+    <row r="51" spans="58:58">
+      <c r="BF51" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="56" spans="57:57">
-      <c r="BE56" t="s">
+    <row r="52" spans="58:58">
+      <c r="BF52" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="57" spans="57:57">
-      <c r="BE57" t="s">
+    <row r="53" spans="58:58">
+      <c r="BF53" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="58" spans="57:57">
-      <c r="BE58" t="s">
+    <row r="54" spans="58:58">
+      <c r="BF54" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="59" spans="57:57">
-      <c r="BE59" t="s">
+    <row r="55" spans="58:58">
+      <c r="BF55" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="60" spans="57:57">
-      <c r="BE60" t="s">
+    <row r="56" spans="58:58">
+      <c r="BF56" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="61" spans="57:57">
-      <c r="BE61" t="s">
+    <row r="57" spans="58:58">
+      <c r="BF57" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="62" spans="57:57">
-      <c r="BE62" t="s">
+    <row r="58" spans="58:58">
+      <c r="BF58" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="63" spans="57:57">
-      <c r="BE63" t="s">
+    <row r="59" spans="58:58">
+      <c r="BF59" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="64" spans="57:57">
-      <c r="BE64" t="s">
+    <row r="60" spans="58:58">
+      <c r="BF60" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="65" spans="57:57">
-      <c r="BE65" t="s">
+    <row r="61" spans="58:58">
+      <c r="BF61" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="66" spans="57:57">
-      <c r="BE66" t="s">
+    <row r="62" spans="58:58">
+      <c r="BF62" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="67" spans="57:57">
-      <c r="BE67" t="s">
+    <row r="63" spans="58:58">
+      <c r="BF63" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="68" spans="57:57">
-      <c r="BE68" t="s">
+    <row r="64" spans="58:58">
+      <c r="BF64" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="69" spans="57:57">
-      <c r="BE69" t="s">
+    <row r="65" spans="58:58">
+      <c r="BF65" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="57:57">
-      <c r="BE70" t="s">
+    <row r="66" spans="58:58">
+      <c r="BF66" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="71" spans="57:57">
-      <c r="BE71" t="s">
+    <row r="67" spans="58:58">
+      <c r="BF67" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="72" spans="57:57">
-      <c r="BE72" t="s">
+    <row r="68" spans="58:58">
+      <c r="BF68" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="73" spans="57:57">
-      <c r="BE73" t="s">
+    <row r="69" spans="58:58">
+      <c r="BF69" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="74" spans="57:57">
-      <c r="BE74" t="s">
+    <row r="70" spans="58:58">
+      <c r="BF70" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="75" spans="57:57">
-      <c r="BE75" t="s">
+    <row r="71" spans="58:58">
+      <c r="BF71" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="76" spans="57:57">
-      <c r="BE76" t="s">
+    <row r="72" spans="58:58">
+      <c r="BF72" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="57:57">
-      <c r="BE77" t="s">
+    <row r="73" spans="58:58">
+      <c r="BF73" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="78" spans="57:57">
-      <c r="BE78" t="s">
+    <row r="74" spans="58:58">
+      <c r="BF74" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="79" spans="57:57">
-      <c r="BE79" t="s">
+    <row r="75" spans="58:58">
+      <c r="BF75" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="80" spans="57:57">
-      <c r="BE80" t="s">
+    <row r="76" spans="58:58">
+      <c r="BF76" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="57:57">
-      <c r="BE81" t="s">
+    <row r="77" spans="58:58">
+      <c r="BF77" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="82" spans="57:57">
-      <c r="BE82" t="s">
+    <row r="78" spans="58:58">
+      <c r="BF78" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="83" spans="57:57">
-      <c r="BE83" t="s">
+    <row r="79" spans="58:58">
+      <c r="BF79" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="84" spans="57:57">
-      <c r="BE84" t="s">
+    <row r="80" spans="58:58">
+      <c r="BF80" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="85" spans="57:57">
-      <c r="BE85" t="s">
+    <row r="81" spans="58:58">
+      <c r="BF81" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="86" spans="57:57">
-      <c r="BE86" t="s">
+    <row r="82" spans="58:58">
+      <c r="BF82" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="87" spans="57:57">
-      <c r="BE87" t="s">
+    <row r="83" spans="58:58">
+      <c r="BF83" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="88" spans="57:57">
-      <c r="BE88" t="s">
+    <row r="84" spans="58:58">
+      <c r="BF84" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="57:57">
-      <c r="BE89" t="s">
+    <row r="85" spans="58:58">
+      <c r="BF85" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="90" spans="57:57">
-      <c r="BE90" t="s">
+    <row r="86" spans="58:58">
+      <c r="BF86" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="91" spans="57:57">
-      <c r="BE91" t="s">
+    <row r="87" spans="58:58">
+      <c r="BF87" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="92" spans="57:57">
-      <c r="BE92" t="s">
+    <row r="88" spans="58:58">
+      <c r="BF88" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="93" spans="57:57">
-      <c r="BE93" t="s">
+    <row r="89" spans="58:58">
+      <c r="BF89" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="94" spans="57:57">
-      <c r="BE94" t="s">
+    <row r="90" spans="58:58">
+      <c r="BF90" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="95" spans="57:57">
-      <c r="BE95" t="s">
+    <row r="91" spans="58:58">
+      <c r="BF91" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="96" spans="57:57">
-      <c r="BE96" t="s">
+    <row r="92" spans="58:58">
+      <c r="BF92" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="97" spans="57:57">
-      <c r="BE97" t="s">
+    <row r="93" spans="58:58">
+      <c r="BF93" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="57:57">
-      <c r="BE98" t="s">
+    <row r="94" spans="58:58">
+      <c r="BF94" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="99" spans="57:57">
-      <c r="BE99" t="s">
+    <row r="95" spans="58:58">
+      <c r="BF95" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="100" spans="57:57">
-      <c r="BE100" t="s">
+    <row r="96" spans="58:58">
+      <c r="BF96" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="101" spans="57:57">
-      <c r="BE101" t="s">
+    <row r="97" spans="58:58">
+      <c r="BF97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="102" spans="57:57">
-      <c r="BE102" t="s">
+    <row r="98" spans="58:58">
+      <c r="BF98" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="103" spans="57:57">
-      <c r="BE103" t="s">
+    <row r="99" spans="58:58">
+      <c r="BF99" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="104" spans="57:57">
-      <c r="BE104" t="s">
+    <row r="100" spans="58:58">
+      <c r="BF100" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="105" spans="57:57">
-      <c r="BE105" t="s">
+    <row r="101" spans="58:58">
+      <c r="BF101" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="106" spans="57:57">
-      <c r="BE106" t="s">
+    <row r="102" spans="58:58">
+      <c r="BF102" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="107" spans="57:57">
-      <c r="BE107" t="s">
+    <row r="103" spans="58:58">
+      <c r="BF103" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="108" spans="57:57">
-      <c r="BE108" t="s">
+    <row r="104" spans="58:58">
+      <c r="BF104" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="109" spans="57:57">
-      <c r="BE109" t="s">
+    <row r="105" spans="58:58">
+      <c r="BF105" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="110" spans="57:57">
-      <c r="BE110" t="s">
+    <row r="106" spans="58:58">
+      <c r="BF106" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="111" spans="57:57">
-      <c r="BE111" t="s">
+    <row r="107" spans="58:58">
+      <c r="BF107" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="112" spans="57:57">
-      <c r="BE112" t="s">
+    <row r="108" spans="58:58">
+      <c r="BF108" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="113" spans="57:57">
-      <c r="BE113" t="s">
+    <row r="109" spans="58:58">
+      <c r="BF109" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="114" spans="57:57">
-      <c r="BE114" t="s">
+    <row r="110" spans="58:58">
+      <c r="BF110" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="115" spans="57:57">
-      <c r="BE115" t="s">
+    <row r="111" spans="58:58">
+      <c r="BF111" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="116" spans="57:57">
-      <c r="BE116" t="s">
+    <row r="112" spans="58:58">
+      <c r="BF112" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="117" spans="57:57">
-      <c r="BE117" t="s">
+    <row r="113" spans="58:58">
+      <c r="BF113" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="118" spans="57:57">
-      <c r="BE118" t="s">
+    <row r="114" spans="58:58">
+      <c r="BF114" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="119" spans="57:57">
-      <c r="BE119" t="s">
+    <row r="115" spans="58:58">
+      <c r="BF115" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="120" spans="57:57">
-      <c r="BE120" t="s">
+    <row r="116" spans="58:58">
+      <c r="BF116" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="121" spans="57:57">
-      <c r="BE121" t="s">
+    <row r="117" spans="58:58">
+      <c r="BF117" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="122" spans="57:57">
-      <c r="BE122" t="s">
+    <row r="118" spans="58:58">
+      <c r="BF118" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="123" spans="57:57">
-      <c r="BE123" t="s">
+    <row r="119" spans="58:58">
+      <c r="BF119" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="124" spans="57:57">
-      <c r="BE124" t="s">
+    <row r="120" spans="58:58">
+      <c r="BF120" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="125" spans="57:57">
-      <c r="BE125" t="s">
+    <row r="121" spans="58:58">
+      <c r="BF121" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="126" spans="57:57">
-      <c r="BE126" t="s">
+    <row r="122" spans="58:58">
+      <c r="BF122" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="127" spans="57:57">
-      <c r="BE127" t="s">
+    <row r="123" spans="58:58">
+      <c r="BF123" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="128" spans="57:57">
-      <c r="BE128" t="s">
+    <row r="124" spans="58:58">
+      <c r="BF124" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="129" spans="57:57">
-      <c r="BE129" t="s">
+    <row r="125" spans="58:58">
+      <c r="BF125" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="130" spans="57:57">
-      <c r="BE130" t="s">
+    <row r="126" spans="58:58">
+      <c r="BF126" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="131" spans="57:57">
-      <c r="BE131" t="s">
+    <row r="127" spans="58:58">
+      <c r="BF127" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="132" spans="57:57">
-      <c r="BE132" t="s">
+    <row r="128" spans="58:58">
+      <c r="BF128" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="133" spans="57:57">
-      <c r="BE133" t="s">
+    <row r="129" spans="58:58">
+      <c r="BF129" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="134" spans="57:57">
-      <c r="BE134" t="s">
+    <row r="130" spans="58:58">
+      <c r="BF130" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="135" spans="57:57">
-      <c r="BE135" t="s">
+    <row r="131" spans="58:58">
+      <c r="BF131" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="136" spans="57:57">
-      <c r="BE136" t="s">
+    <row r="132" spans="58:58">
+      <c r="BF132" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="137" spans="57:57">
-      <c r="BE137" t="s">
+    <row r="133" spans="58:58">
+      <c r="BF133" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="138" spans="57:57">
-      <c r="BE138" t="s">
+    <row r="134" spans="58:58">
+      <c r="BF134" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="139" spans="57:57">
-      <c r="BE139" t="s">
+    <row r="135" spans="58:58">
+      <c r="BF135" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="140" spans="57:57">
-      <c r="BE140" t="s">
+    <row r="136" spans="58:58">
+      <c r="BF136" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="141" spans="57:57">
-      <c r="BE141" t="s">
+    <row r="137" spans="58:58">
+      <c r="BF137" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="142" spans="57:57">
-      <c r="BE142" t="s">
+    <row r="138" spans="58:58">
+      <c r="BF138" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="143" spans="57:57">
-      <c r="BE143" t="s">
+    <row r="139" spans="58:58">
+      <c r="BF139" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="144" spans="57:57">
-      <c r="BE144" t="s">
+    <row r="140" spans="58:58">
+      <c r="BF140" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="145" spans="57:57">
-      <c r="BE145" t="s">
+    <row r="141" spans="58:58">
+      <c r="BF141" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="146" spans="57:57">
-      <c r="BE146" t="s">
+    <row r="142" spans="58:58">
+      <c r="BF142" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="147" spans="57:57">
-      <c r="BE147" t="s">
+    <row r="143" spans="58:58">
+      <c r="BF143" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="148" spans="57:57">
-      <c r="BE148" t="s">
+    <row r="144" spans="58:58">
+      <c r="BF144" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="149" spans="57:57">
-      <c r="BE149" t="s">
+    <row r="145" spans="58:58">
+      <c r="BF145" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="150" spans="57:57">
-      <c r="BE150" t="s">
+    <row r="146" spans="58:58">
+      <c r="BF146" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="151" spans="57:57">
-      <c r="BE151" t="s">
+    <row r="147" spans="58:58">
+      <c r="BF147" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="152" spans="57:57">
-      <c r="BE152" t="s">
+    <row r="148" spans="58:58">
+      <c r="BF148" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="153" spans="57:57">
-      <c r="BE153" t="s">
+    <row r="149" spans="58:58">
+      <c r="BF149" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="154" spans="57:57">
-      <c r="BE154" t="s">
+    <row r="150" spans="58:58">
+      <c r="BF150" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="155" spans="57:57">
-      <c r="BE155" t="s">
+    <row r="151" spans="58:58">
+      <c r="BF151" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="156" spans="57:57">
-      <c r="BE156" t="s">
+    <row r="152" spans="58:58">
+      <c r="BF152" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="157" spans="57:57">
-      <c r="BE157" t="s">
+    <row r="153" spans="58:58">
+      <c r="BF153" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="158" spans="57:57">
-      <c r="BE158" t="s">
+    <row r="154" spans="58:58">
+      <c r="BF154" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="159" spans="57:57">
-      <c r="BE159" t="s">
+    <row r="155" spans="58:58">
+      <c r="BF155" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="160" spans="57:57">
-      <c r="BE160" t="s">
+    <row r="156" spans="58:58">
+      <c r="BF156" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="161" spans="57:57">
-      <c r="BE161" t="s">
+    <row r="157" spans="58:58">
+      <c r="BF157" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="162" spans="57:57">
-      <c r="BE162" t="s">
+    <row r="158" spans="58:58">
+      <c r="BF158" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="163" spans="57:57">
-      <c r="BE163" t="s">
+    <row r="159" spans="58:58">
+      <c r="BF159" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="164" spans="57:57">
-      <c r="BE164" t="s">
+    <row r="160" spans="58:58">
+      <c r="BF160" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="165" spans="57:57">
-      <c r="BE165" t="s">
+    <row r="161" spans="58:58">
+      <c r="BF161" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="166" spans="57:57">
-      <c r="BE166" t="s">
+    <row r="162" spans="58:58">
+      <c r="BF162" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="167" spans="57:57">
-      <c r="BE167" t="s">
+    <row r="163" spans="58:58">
+      <c r="BF163" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="168" spans="57:57">
-      <c r="BE168" t="s">
+    <row r="164" spans="58:58">
+      <c r="BF164" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="169" spans="57:57">
-      <c r="BE169" t="s">
+    <row r="165" spans="58:58">
+      <c r="BF165" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="170" spans="57:57">
-      <c r="BE170" t="s">
+    <row r="166" spans="58:58">
+      <c r="BF166" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="171" spans="57:57">
-      <c r="BE171" t="s">
+    <row r="167" spans="58:58">
+      <c r="BF167" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="172" spans="57:57">
-      <c r="BE172" t="s">
+    <row r="168" spans="58:58">
+      <c r="BF168" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="173" spans="57:57">
-      <c r="BE173" t="s">
+    <row r="169" spans="58:58">
+      <c r="BF169" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="174" spans="57:57">
-      <c r="BE174" t="s">
+    <row r="170" spans="58:58">
+      <c r="BF170" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="175" spans="57:57">
-      <c r="BE175" t="s">
+    <row r="171" spans="58:58">
+      <c r="BF171" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="176" spans="57:57">
-      <c r="BE176" t="s">
+    <row r="172" spans="58:58">
+      <c r="BF172" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="177" spans="57:57">
-      <c r="BE177" t="s">
+    <row r="173" spans="58:58">
+      <c r="BF173" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="178" spans="57:57">
-      <c r="BE178" t="s">
+    <row r="174" spans="58:58">
+      <c r="BF174" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="179" spans="57:57">
-      <c r="BE179" t="s">
+    <row r="175" spans="58:58">
+      <c r="BF175" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="180" spans="57:57">
-      <c r="BE180" t="s">
+    <row r="176" spans="58:58">
+      <c r="BF176" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="181" spans="57:57">
-      <c r="BE181" t="s">
+    <row r="177" spans="58:58">
+      <c r="BF177" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="182" spans="57:57">
-      <c r="BE182" t="s">
+    <row r="178" spans="58:58">
+      <c r="BF178" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="183" spans="57:57">
-      <c r="BE183" t="s">
+    <row r="179" spans="58:58">
+      <c r="BF179" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="184" spans="57:57">
-      <c r="BE184" t="s">
+    <row r="180" spans="58:58">
+      <c r="BF180" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="185" spans="57:57">
-      <c r="BE185" t="s">
+    <row r="181" spans="58:58">
+      <c r="BF181" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="186" spans="57:57">
-      <c r="BE186" t="s">
+    <row r="182" spans="58:58">
+      <c r="BF182" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="187" spans="57:57">
-      <c r="BE187" t="s">
+    <row r="183" spans="58:58">
+      <c r="BF183" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="188" spans="57:57">
-      <c r="BE188" t="s">
+    <row r="184" spans="58:58">
+      <c r="BF184" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="189" spans="57:57">
-      <c r="BE189" t="s">
+    <row r="185" spans="58:58">
+      <c r="BF185" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="190" spans="57:57">
-      <c r="BE190" t="s">
+    <row r="186" spans="58:58">
+      <c r="BF186" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="191" spans="57:57">
-      <c r="BE191" t="s">
+    <row r="187" spans="58:58">
+      <c r="BF187" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="192" spans="57:57">
-      <c r="BE192" t="s">
+    <row r="188" spans="58:58">
+      <c r="BF188" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="193" spans="57:57">
-      <c r="BE193" t="s">
+    <row r="189" spans="58:58">
+      <c r="BF189" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="194" spans="57:57">
-      <c r="BE194" t="s">
+    <row r="190" spans="58:58">
+      <c r="BF190" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="195" spans="57:57">
-      <c r="BE195" t="s">
+    <row r="191" spans="58:58">
+      <c r="BF191" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="196" spans="57:57">
-      <c r="BE196" t="s">
+    <row r="192" spans="58:58">
+      <c r="BF192" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="197" spans="57:57">
-      <c r="BE197" t="s">
+    <row r="193" spans="58:58">
+      <c r="BF193" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="198" spans="57:57">
-      <c r="BE198" t="s">
+    <row r="194" spans="58:58">
+      <c r="BF194" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="199" spans="57:57">
-      <c r="BE199" t="s">
+    <row r="195" spans="58:58">
+      <c r="BF195" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="200" spans="57:57">
-      <c r="BE200" t="s">
+    <row r="196" spans="58:58">
+      <c r="BF196" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="201" spans="57:57">
-      <c r="BE201" t="s">
+    <row r="197" spans="58:58">
+      <c r="BF197" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="202" spans="57:57">
-      <c r="BE202" t="s">
+    <row r="198" spans="58:58">
+      <c r="BF198" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="203" spans="57:57">
-      <c r="BE203" t="s">
+    <row r="199" spans="58:58">
+      <c r="BF199" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="204" spans="57:57">
-      <c r="BE204" t="s">
+    <row r="200" spans="58:58">
+      <c r="BF200" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="205" spans="57:57">
-      <c r="BE205" t="s">
+    <row r="201" spans="58:58">
+      <c r="BF201" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="206" spans="57:57">
-      <c r="BE206" t="s">
+    <row r="202" spans="58:58">
+      <c r="BF202" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="207" spans="57:57">
-      <c r="BE207" t="s">
+    <row r="203" spans="58:58">
+      <c r="BF203" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="208" spans="57:57">
-      <c r="BE208" t="s">
+    <row r="204" spans="58:58">
+      <c r="BF204" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="209" spans="57:57">
-      <c r="BE209" t="s">
+    <row r="205" spans="58:58">
+      <c r="BF205" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="210" spans="57:57">
-      <c r="BE210" t="s">
+    <row r="206" spans="58:58">
+      <c r="BF206" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="211" spans="57:57">
-      <c r="BE211" t="s">
+    <row r="207" spans="58:58">
+      <c r="BF207" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="212" spans="57:57">
-      <c r="BE212" t="s">
+    <row r="208" spans="58:58">
+      <c r="BF208" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="213" spans="57:57">
-      <c r="BE213" t="s">
+    <row r="209" spans="58:58">
+      <c r="BF209" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="214" spans="57:57">
-      <c r="BE214" t="s">
+    <row r="210" spans="58:58">
+      <c r="BF210" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="215" spans="57:57">
-      <c r="BE215" t="s">
+    <row r="211" spans="58:58">
+      <c r="BF211" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="216" spans="57:57">
-      <c r="BE216" t="s">
+    <row r="212" spans="58:58">
+      <c r="BF212" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="217" spans="57:57">
-      <c r="BE217" t="s">
+    <row r="213" spans="58:58">
+      <c r="BF213" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="218" spans="57:57">
-      <c r="BE218" t="s">
+    <row r="214" spans="58:58">
+      <c r="BF214" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="219" spans="57:57">
-      <c r="BE219" t="s">
+    <row r="215" spans="58:58">
+      <c r="BF215" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="220" spans="57:57">
-      <c r="BE220" t="s">
+    <row r="216" spans="58:58">
+      <c r="BF216" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="221" spans="57:57">
-      <c r="BE221" t="s">
+    <row r="217" spans="58:58">
+      <c r="BF217" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="222" spans="57:57">
-      <c r="BE222" t="s">
+    <row r="218" spans="58:58">
+      <c r="BF218" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="223" spans="57:57">
-      <c r="BE223" t="s">
+    <row r="219" spans="58:58">
+      <c r="BF219" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="224" spans="57:57">
-      <c r="BE224" t="s">
+    <row r="220" spans="58:58">
+      <c r="BF220" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="225" spans="57:57">
-      <c r="BE225" t="s">
+    <row r="221" spans="58:58">
+      <c r="BF221" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="226" spans="57:57">
-      <c r="BE226" t="s">
+    <row r="222" spans="58:58">
+      <c r="BF222" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="227" spans="57:57">
-      <c r="BE227" t="s">
+    <row r="223" spans="58:58">
+      <c r="BF223" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="228" spans="57:57">
-      <c r="BE228" t="s">
+    <row r="224" spans="58:58">
+      <c r="BF224" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="229" spans="57:57">
-      <c r="BE229" t="s">
+    <row r="225" spans="58:58">
+      <c r="BF225" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="230" spans="57:57">
-      <c r="BE230" t="s">
+    <row r="226" spans="58:58">
+      <c r="BF226" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="231" spans="57:57">
-      <c r="BE231" t="s">
+    <row r="227" spans="58:58">
+      <c r="BF227" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="232" spans="57:57">
-      <c r="BE232" t="s">
+    <row r="228" spans="58:58">
+      <c r="BF228" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="233" spans="57:57">
-      <c r="BE233" t="s">
+    <row r="229" spans="58:58">
+      <c r="BF229" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="234" spans="57:57">
-      <c r="BE234" t="s">
+    <row r="230" spans="58:58">
+      <c r="BF230" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="235" spans="57:57">
-      <c r="BE235" t="s">
+    <row r="231" spans="58:58">
+      <c r="BF231" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="236" spans="57:57">
-      <c r="BE236" t="s">
+    <row r="232" spans="58:58">
+      <c r="BF232" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="237" spans="57:57">
-      <c r="BE237" t="s">
+    <row r="233" spans="58:58">
+      <c r="BF233" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="238" spans="57:57">
-      <c r="BE238" t="s">
+    <row r="234" spans="58:58">
+      <c r="BF234" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="239" spans="57:57">
-      <c r="BE239" t="s">
+    <row r="235" spans="58:58">
+      <c r="BF235" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="240" spans="57:57">
-      <c r="BE240" t="s">
+    <row r="236" spans="58:58">
+      <c r="BF236" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="241" spans="57:57">
-      <c r="BE241" t="s">
+    <row r="237" spans="58:58">
+      <c r="BF237" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="242" spans="57:57">
-      <c r="BE242" t="s">
+    <row r="238" spans="58:58">
+      <c r="BF238" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="243" spans="57:57">
-      <c r="BE243" t="s">
+    <row r="239" spans="58:58">
+      <c r="BF239" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="244" spans="57:57">
-      <c r="BE244" t="s">
+    <row r="240" spans="58:58">
+      <c r="BF240" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="245" spans="57:57">
-      <c r="BE245" t="s">
+    <row r="241" spans="58:58">
+      <c r="BF241" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="246" spans="57:57">
-      <c r="BE246" t="s">
+    <row r="242" spans="58:58">
+      <c r="BF242" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="247" spans="57:57">
-      <c r="BE247" t="s">
+    <row r="243" spans="58:58">
+      <c r="BF243" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="248" spans="57:57">
-      <c r="BE248" t="s">
+    <row r="244" spans="58:58">
+      <c r="BF244" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="249" spans="57:57">
-      <c r="BE249" t="s">
+    <row r="245" spans="58:58">
+      <c r="BF245" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="250" spans="57:57">
-      <c r="BE250" t="s">
+    <row r="246" spans="58:58">
+      <c r="BF246" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="251" spans="57:57">
-      <c r="BE251" t="s">
+    <row r="247" spans="58:58">
+      <c r="BF247" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="252" spans="57:57">
-      <c r="BE252" t="s">
+    <row r="248" spans="58:58">
+      <c r="BF248" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="253" spans="57:57">
-      <c r="BE253" t="s">
+    <row r="249" spans="58:58">
+      <c r="BF249" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="254" spans="57:57">
-      <c r="BE254" t="s">
+    <row r="250" spans="58:58">
+      <c r="BF250" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="255" spans="57:57">
-      <c r="BE255" t="s">
+    <row r="251" spans="58:58">
+      <c r="BF251" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="256" spans="57:57">
-      <c r="BE256" t="s">
+    <row r="252" spans="58:58">
+      <c r="BF252" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="257" spans="57:57">
-      <c r="BE257" t="s">
+    <row r="253" spans="58:58">
+      <c r="BF253" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="258" spans="57:57">
-      <c r="BE258" t="s">
+    <row r="254" spans="58:58">
+      <c r="BF254" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="259" spans="57:57">
-      <c r="BE259" t="s">
+    <row r="255" spans="58:58">
+      <c r="BF255" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="260" spans="57:57">
-      <c r="BE260" t="s">
+    <row r="256" spans="58:58">
+      <c r="BF256" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="261" spans="57:57">
-      <c r="BE261" t="s">
+    <row r="257" spans="58:58">
+      <c r="BF257" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="262" spans="57:57">
-      <c r="BE262" t="s">
+    <row r="258" spans="58:58">
+      <c r="BF258" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="263" spans="57:57">
-      <c r="BE263" t="s">
+    <row r="259" spans="58:58">
+      <c r="BF259" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="264" spans="57:57">
-      <c r="BE264" t="s">
+    <row r="260" spans="58:58">
+      <c r="BF260" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="265" spans="57:57">
-      <c r="BE265" t="s">
+    <row r="261" spans="58:58">
+      <c r="BF261" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="266" spans="57:57">
-      <c r="BE266" t="s">
+    <row r="262" spans="58:58">
+      <c r="BF262" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="267" spans="57:57">
-      <c r="BE267" t="s">
+    <row r="263" spans="58:58">
+      <c r="BF263" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="268" spans="57:57">
-      <c r="BE268" t="s">
+    <row r="264" spans="58:58">
+      <c r="BF264" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="269" spans="57:57">
-      <c r="BE269" t="s">
+    <row r="265" spans="58:58">
+      <c r="BF265" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="270" spans="57:57">
-      <c r="BE270" t="s">
+    <row r="266" spans="58:58">
+      <c r="BF266" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="271" spans="57:57">
-      <c r="BE271" t="s">
+    <row r="267" spans="58:58">
+      <c r="BF267" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="272" spans="57:57">
-      <c r="BE272" t="s">
+    <row r="268" spans="58:58">
+      <c r="BF268" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="273" spans="57:57">
-      <c r="BE273" t="s">
+    <row r="269" spans="58:58">
+      <c r="BF269" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="274" spans="57:57">
-      <c r="BE274" t="s">
+    <row r="270" spans="58:58">
+      <c r="BF270" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="275" spans="57:57">
-      <c r="BE275" t="s">
+    <row r="271" spans="58:58">
+      <c r="BF271" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="276" spans="57:57">
-      <c r="BE276" t="s">
+    <row r="272" spans="58:58">
+      <c r="BF272" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="277" spans="57:57">
-      <c r="BE277" t="s">
+    <row r="273" spans="58:58">
+      <c r="BF273" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="278" spans="57:57">
-      <c r="BE278" t="s">
+    <row r="274" spans="58:58">
+      <c r="BF274" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="279" spans="57:57">
-      <c r="BE279" t="s">
+    <row r="275" spans="58:58">
+      <c r="BF275" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="280" spans="57:57">
-      <c r="BE280" t="s">
+    <row r="276" spans="58:58">
+      <c r="BF276" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="281" spans="57:57">
-      <c r="BE281" t="s">
+    <row r="277" spans="58:58">
+      <c r="BF277" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="282" spans="57:57">
-      <c r="BE282" t="s">
+    <row r="278" spans="58:58">
+      <c r="BF278" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="283" spans="57:57">
-      <c r="BE283" t="s">
+    <row r="279" spans="58:58">
+      <c r="BF279" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="284" spans="57:57">
-      <c r="BE284" t="s">
+    <row r="280" spans="58:58">
+      <c r="BF280" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="285" spans="57:57">
-      <c r="BE285" t="s">
+    <row r="281" spans="58:58">
+      <c r="BF281" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="286" spans="57:57">
-      <c r="BE286" t="s">
+    <row r="282" spans="58:58">
+      <c r="BF282" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="287" spans="57:57">
-      <c r="BE287" t="s">
+    <row r="283" spans="58:58">
+      <c r="BF283" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="288" spans="57:57">
-      <c r="BE288" t="s">
+    <row r="284" spans="58:58">
+      <c r="BF284" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="289" spans="57:57">
-      <c r="BE289" t="s">
+    <row r="285" spans="58:58">
+      <c r="BF285" t="s">
         <v>711</v>
+      </c>
+    </row>
+    <row r="286" spans="58:58">
+      <c r="BF286" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="287" spans="58:58">
+      <c r="BF287" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="288" spans="58:58">
+      <c r="BF288" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="289" spans="58:58">
+      <c r="BF289" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="290" spans="58:58">
+      <c r="BF290" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="291" spans="58:58">
+      <c r="BF291" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="292" spans="58:58">
+      <c r="BF292" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="293" spans="58:58">
+      <c r="BF293" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="294" spans="58:58">
+      <c r="BF294" t="s">
+        <v>720</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -18,26 +18,26 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BF$1:$BF$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$V$1:$V$2</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$W$1:$W$2</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AG$1:$AG$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DT$1:$DT$4</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AH$1:$AH$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DU$1:$DU$4</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$H$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="918">
   <si>
     <t>alias</t>
   </si>
@@ -853,6 +853,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4308,13 +4314,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EW2"/>
+  <dimension ref="A1:EX2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:153">
+    <row r="1" spans="1:154">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4334,16 +4340,16 @@
         <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>326</v>
@@ -4379,7 +4385,7 @@
         <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>352</v>
@@ -4412,7 +4418,7 @@
         <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>377</v>
@@ -4424,7 +4430,7 @@
         <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>387</v>
@@ -4487,7 +4493,7 @@
         <v>425</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>721</v>
+        <v>427</v>
       </c>
       <c r="BG1" s="1" t="s">
         <v>723</v>
@@ -4685,7 +4691,7 @@
         <v>851</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="DU1" s="1" t="s">
         <v>859</v>
@@ -4730,7 +4736,7 @@
         <v>885</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="EJ1" s="1" t="s">
         <v>888</v>
@@ -4774,8 +4780,11 @@
       <c r="EW1" s="1" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="2" spans="1:153" ht="150" customHeight="1">
+      <c r="EX1" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="2" spans="1:154" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4795,16 +4804,16 @@
         <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>327</v>
@@ -4840,7 +4849,7 @@
         <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>353</v>
@@ -4873,7 +4882,7 @@
         <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
         <v>378</v>
@@ -4885,7 +4894,7 @@
         <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
         <v>388</v>
@@ -4948,7 +4957,7 @@
         <v>426</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>722</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="2" t="s">
         <v>724</v>
@@ -5146,7 +5155,7 @@
         <v>852</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="DU2" s="2" t="s">
         <v>860</v>
@@ -5188,10 +5197,10 @@
         <v>884</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>806</v>
+        <v>886</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>887</v>
+        <v>808</v>
       </c>
       <c r="EJ2" s="2" t="s">
         <v>889</v>
@@ -5235,31 +5244,34 @@
       <c r="EW2" s="2" t="s">
         <v>915</v>
       </c>
+      <c r="EX2" s="2" t="s">
+        <v>917</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3:AG101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK3:AK101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL3:AL101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG3:BG101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DT3:DT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DU3:DU101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -5269,1636 +5281,1636 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:DT294"/>
+  <dimension ref="H1:DU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:124">
-      <c r="G1" t="s">
-        <v>276</v>
-      </c>
+    <row r="1" spans="8:125">
       <c r="H1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J1" t="s">
-        <v>317</v>
-      </c>
-      <c r="V1" t="s">
-        <v>348</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>372</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>383</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>427</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="2" spans="7:124">
-      <c r="G2" t="s">
-        <v>277</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="I1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K1" t="s">
+        <v>319</v>
+      </c>
+      <c r="W1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>374</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>385</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>429</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="2" spans="8:125">
       <c r="H2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J2" t="s">
-        <v>318</v>
-      </c>
-      <c r="V2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>373</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>428</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="3" spans="7:124">
-      <c r="G3" t="s">
-        <v>278</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="I2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" t="s">
+        <v>320</v>
+      </c>
+      <c r="W2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>375</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>386</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>430</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="3" spans="8:125">
       <c r="H3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J3" t="s">
-        <v>319</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>374</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>429</v>
-      </c>
-      <c r="DT3" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="4" spans="7:124">
-      <c r="G4" t="s">
-        <v>279</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="I3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K3" t="s">
+        <v>321</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>376</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>431</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="4" spans="8:125">
       <c r="H4" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" t="s">
-        <v>320</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>430</v>
-      </c>
-      <c r="DT4" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="5" spans="7:124">
-      <c r="G5" t="s">
-        <v>280</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="I4" t="s">
+        <v>313</v>
+      </c>
+      <c r="K4" t="s">
+        <v>322</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>432</v>
+      </c>
+      <c r="DU4" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="5" spans="8:125">
       <c r="H5" t="s">
-        <v>312</v>
-      </c>
-      <c r="J5" t="s">
-        <v>321</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="6" spans="7:124">
-      <c r="G6" t="s">
-        <v>281</v>
-      </c>
-      <c r="J6" t="s">
-        <v>322</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="7:124">
-      <c r="G7" t="s">
         <v>282</v>
       </c>
-      <c r="J7" t="s">
+      <c r="I5" t="s">
+        <v>314</v>
+      </c>
+      <c r="K5" t="s">
         <v>323</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG5" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="8" spans="7:124">
-      <c r="G8" t="s">
+    <row r="6" spans="8:125">
+      <c r="H6" t="s">
         <v>283</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="K6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG6" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="9" spans="7:124">
-      <c r="G9" t="s">
+    <row r="7" spans="8:125">
+      <c r="H7" t="s">
         <v>284</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="K7" t="s">
+        <v>325</v>
+      </c>
+      <c r="BG7" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="10" spans="7:124">
-      <c r="G10" t="s">
+    <row r="8" spans="8:125">
+      <c r="H8" t="s">
         <v>285</v>
       </c>
-      <c r="BF10" t="s">
+      <c r="BG8" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="11" spans="7:124">
-      <c r="G11" t="s">
+    <row r="9" spans="8:125">
+      <c r="H9" t="s">
         <v>286</v>
       </c>
-      <c r="BF11" t="s">
+      <c r="BG9" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="12" spans="7:124">
-      <c r="G12" t="s">
+    <row r="10" spans="8:125">
+      <c r="H10" t="s">
         <v>287</v>
       </c>
-      <c r="BF12" t="s">
+      <c r="BG10" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="13" spans="7:124">
-      <c r="G13" t="s">
+    <row r="11" spans="8:125">
+      <c r="H11" t="s">
         <v>288</v>
       </c>
-      <c r="BF13" t="s">
+      <c r="BG11" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="14" spans="7:124">
-      <c r="G14" t="s">
+    <row r="12" spans="8:125">
+      <c r="H12" t="s">
         <v>289</v>
       </c>
-      <c r="BF14" t="s">
+      <c r="BG12" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="15" spans="7:124">
-      <c r="G15" t="s">
+    <row r="13" spans="8:125">
+      <c r="H13" t="s">
         <v>290</v>
       </c>
-      <c r="BF15" t="s">
+      <c r="BG13" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="16" spans="7:124">
-      <c r="G16" t="s">
+    <row r="14" spans="8:125">
+      <c r="H14" t="s">
         <v>291</v>
       </c>
-      <c r="BF16" t="s">
+      <c r="BG14" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="17" spans="7:58">
-      <c r="G17" t="s">
+    <row r="15" spans="8:125">
+      <c r="H15" t="s">
         <v>292</v>
       </c>
-      <c r="BF17" t="s">
+      <c r="BG15" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="18" spans="7:58">
-      <c r="G18" t="s">
+    <row r="16" spans="8:125">
+      <c r="H16" t="s">
         <v>293</v>
       </c>
-      <c r="BF18" t="s">
+      <c r="BG16" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="19" spans="7:58">
-      <c r="G19" t="s">
+    <row r="17" spans="8:59">
+      <c r="H17" t="s">
         <v>294</v>
       </c>
-      <c r="BF19" t="s">
+      <c r="BG17" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="20" spans="7:58">
-      <c r="G20" t="s">
+    <row r="18" spans="8:59">
+      <c r="H18" t="s">
         <v>295</v>
       </c>
-      <c r="BF20" t="s">
+      <c r="BG18" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="21" spans="7:58">
-      <c r="G21" t="s">
+    <row r="19" spans="8:59">
+      <c r="H19" t="s">
         <v>296</v>
       </c>
-      <c r="BF21" t="s">
+      <c r="BG19" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="22" spans="7:58">
-      <c r="G22" t="s">
+    <row r="20" spans="8:59">
+      <c r="H20" t="s">
         <v>297</v>
       </c>
-      <c r="BF22" t="s">
+      <c r="BG20" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="7:58">
-      <c r="G23" t="s">
+    <row r="21" spans="8:59">
+      <c r="H21" t="s">
         <v>298</v>
       </c>
-      <c r="BF23" t="s">
+      <c r="BG21" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="24" spans="7:58">
-      <c r="G24" t="s">
+    <row r="22" spans="8:59">
+      <c r="H22" t="s">
         <v>299</v>
       </c>
-      <c r="BF24" t="s">
+      <c r="BG22" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="25" spans="7:58">
-      <c r="G25" t="s">
+    <row r="23" spans="8:59">
+      <c r="H23" t="s">
         <v>300</v>
       </c>
-      <c r="BF25" t="s">
+      <c r="BG23" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="26" spans="7:58">
-      <c r="G26" t="s">
+    <row r="24" spans="8:59">
+      <c r="H24" t="s">
         <v>301</v>
       </c>
-      <c r="BF26" t="s">
+      <c r="BG24" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="27" spans="7:58">
-      <c r="G27" t="s">
+    <row r="25" spans="8:59">
+      <c r="H25" t="s">
         <v>302</v>
       </c>
-      <c r="BF27" t="s">
+      <c r="BG25" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="28" spans="7:58">
-      <c r="G28" t="s">
+    <row r="26" spans="8:59">
+      <c r="H26" t="s">
         <v>303</v>
       </c>
-      <c r="BF28" t="s">
+      <c r="BG26" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="29" spans="7:58">
-      <c r="G29" t="s">
+    <row r="27" spans="8:59">
+      <c r="H27" t="s">
         <v>304</v>
       </c>
-      <c r="BF29" t="s">
+      <c r="BG27" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="30" spans="7:58">
-      <c r="G30" t="s">
+    <row r="28" spans="8:59">
+      <c r="H28" t="s">
         <v>305</v>
       </c>
-      <c r="BF30" t="s">
+      <c r="BG28" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="31" spans="7:58">
-      <c r="BF31" t="s">
+    <row r="29" spans="8:59">
+      <c r="H29" t="s">
+        <v>306</v>
+      </c>
+      <c r="BG29" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="32" spans="7:58">
-      <c r="BF32" t="s">
+    <row r="30" spans="8:59">
+      <c r="H30" t="s">
+        <v>307</v>
+      </c>
+      <c r="BG30" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="33" spans="58:58">
-      <c r="BF33" t="s">
+    <row r="31" spans="8:59">
+      <c r="BG31" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="34" spans="58:58">
-      <c r="BF34" t="s">
+    <row r="32" spans="8:59">
+      <c r="BG32" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="35" spans="58:58">
-      <c r="BF35" t="s">
+    <row r="33" spans="59:59">
+      <c r="BG33" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="36" spans="58:58">
-      <c r="BF36" t="s">
+    <row r="34" spans="59:59">
+      <c r="BG34" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="37" spans="58:58">
-      <c r="BF37" t="s">
+    <row r="35" spans="59:59">
+      <c r="BG35" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="38" spans="58:58">
-      <c r="BF38" t="s">
+    <row r="36" spans="59:59">
+      <c r="BG36" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="39" spans="58:58">
-      <c r="BF39" t="s">
+    <row r="37" spans="59:59">
+      <c r="BG37" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="40" spans="58:58">
-      <c r="BF40" t="s">
+    <row r="38" spans="59:59">
+      <c r="BG38" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="41" spans="58:58">
-      <c r="BF41" t="s">
+    <row r="39" spans="59:59">
+      <c r="BG39" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="42" spans="58:58">
-      <c r="BF42" t="s">
+    <row r="40" spans="59:59">
+      <c r="BG40" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="43" spans="58:58">
-      <c r="BF43" t="s">
+    <row r="41" spans="59:59">
+      <c r="BG41" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="44" spans="58:58">
-      <c r="BF44" t="s">
+    <row r="42" spans="59:59">
+      <c r="BG42" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="45" spans="58:58">
-      <c r="BF45" t="s">
+    <row r="43" spans="59:59">
+      <c r="BG43" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="46" spans="58:58">
-      <c r="BF46" t="s">
+    <row r="44" spans="59:59">
+      <c r="BG44" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="47" spans="58:58">
-      <c r="BF47" t="s">
+    <row r="45" spans="59:59">
+      <c r="BG45" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="48" spans="58:58">
-      <c r="BF48" t="s">
+    <row r="46" spans="59:59">
+      <c r="BG46" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="49" spans="58:58">
-      <c r="BF49" t="s">
+    <row r="47" spans="59:59">
+      <c r="BG47" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="50" spans="58:58">
-      <c r="BF50" t="s">
+    <row r="48" spans="59:59">
+      <c r="BG48" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="51" spans="58:58">
-      <c r="BF51" t="s">
+    <row r="49" spans="59:59">
+      <c r="BG49" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="52" spans="58:58">
-      <c r="BF52" t="s">
+    <row r="50" spans="59:59">
+      <c r="BG50" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="53" spans="58:58">
-      <c r="BF53" t="s">
+    <row r="51" spans="59:59">
+      <c r="BG51" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="54" spans="58:58">
-      <c r="BF54" t="s">
+    <row r="52" spans="59:59">
+      <c r="BG52" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="55" spans="58:58">
-      <c r="BF55" t="s">
+    <row r="53" spans="59:59">
+      <c r="BG53" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="56" spans="58:58">
-      <c r="BF56" t="s">
+    <row r="54" spans="59:59">
+      <c r="BG54" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="57" spans="58:58">
-      <c r="BF57" t="s">
+    <row r="55" spans="59:59">
+      <c r="BG55" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="58" spans="58:58">
-      <c r="BF58" t="s">
+    <row r="56" spans="59:59">
+      <c r="BG56" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="59" spans="58:58">
-      <c r="BF59" t="s">
+    <row r="57" spans="59:59">
+      <c r="BG57" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="60" spans="58:58">
-      <c r="BF60" t="s">
+    <row r="58" spans="59:59">
+      <c r="BG58" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="61" spans="58:58">
-      <c r="BF61" t="s">
+    <row r="59" spans="59:59">
+      <c r="BG59" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="62" spans="58:58">
-      <c r="BF62" t="s">
+    <row r="60" spans="59:59">
+      <c r="BG60" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="63" spans="58:58">
-      <c r="BF63" t="s">
+    <row r="61" spans="59:59">
+      <c r="BG61" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="64" spans="58:58">
-      <c r="BF64" t="s">
+    <row r="62" spans="59:59">
+      <c r="BG62" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="65" spans="58:58">
-      <c r="BF65" t="s">
+    <row r="63" spans="59:59">
+      <c r="BG63" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="66" spans="58:58">
-      <c r="BF66" t="s">
+    <row r="64" spans="59:59">
+      <c r="BG64" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="67" spans="58:58">
-      <c r="BF67" t="s">
+    <row r="65" spans="59:59">
+      <c r="BG65" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="68" spans="58:58">
-      <c r="BF68" t="s">
+    <row r="66" spans="59:59">
+      <c r="BG66" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="69" spans="58:58">
-      <c r="BF69" t="s">
+    <row r="67" spans="59:59">
+      <c r="BG67" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="70" spans="58:58">
-      <c r="BF70" t="s">
+    <row r="68" spans="59:59">
+      <c r="BG68" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="71" spans="58:58">
-      <c r="BF71" t="s">
+    <row r="69" spans="59:59">
+      <c r="BG69" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="72" spans="58:58">
-      <c r="BF72" t="s">
+    <row r="70" spans="59:59">
+      <c r="BG70" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="73" spans="58:58">
-      <c r="BF73" t="s">
+    <row r="71" spans="59:59">
+      <c r="BG71" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="74" spans="58:58">
-      <c r="BF74" t="s">
+    <row r="72" spans="59:59">
+      <c r="BG72" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="75" spans="58:58">
-      <c r="BF75" t="s">
+    <row r="73" spans="59:59">
+      <c r="BG73" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="76" spans="58:58">
-      <c r="BF76" t="s">
+    <row r="74" spans="59:59">
+      <c r="BG74" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="77" spans="58:58">
-      <c r="BF77" t="s">
+    <row r="75" spans="59:59">
+      <c r="BG75" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="78" spans="58:58">
-      <c r="BF78" t="s">
+    <row r="76" spans="59:59">
+      <c r="BG76" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="79" spans="58:58">
-      <c r="BF79" t="s">
+    <row r="77" spans="59:59">
+      <c r="BG77" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="80" spans="58:58">
-      <c r="BF80" t="s">
+    <row r="78" spans="59:59">
+      <c r="BG78" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="81" spans="58:58">
-      <c r="BF81" t="s">
+    <row r="79" spans="59:59">
+      <c r="BG79" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="82" spans="58:58">
-      <c r="BF82" t="s">
+    <row r="80" spans="59:59">
+      <c r="BG80" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="58:58">
-      <c r="BF83" t="s">
+    <row r="81" spans="59:59">
+      <c r="BG81" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="58:58">
-      <c r="BF84" t="s">
+    <row r="82" spans="59:59">
+      <c r="BG82" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="85" spans="58:58">
-      <c r="BF85" t="s">
+    <row r="83" spans="59:59">
+      <c r="BG83" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="86" spans="58:58">
-      <c r="BF86" t="s">
+    <row r="84" spans="59:59">
+      <c r="BG84" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="87" spans="58:58">
-      <c r="BF87" t="s">
+    <row r="85" spans="59:59">
+      <c r="BG85" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="88" spans="58:58">
-      <c r="BF88" t="s">
+    <row r="86" spans="59:59">
+      <c r="BG86" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="89" spans="58:58">
-      <c r="BF89" t="s">
+    <row r="87" spans="59:59">
+      <c r="BG87" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="90" spans="58:58">
-      <c r="BF90" t="s">
+    <row r="88" spans="59:59">
+      <c r="BG88" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="58:58">
-      <c r="BF91" t="s">
+    <row r="89" spans="59:59">
+      <c r="BG89" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="92" spans="58:58">
-      <c r="BF92" t="s">
+    <row r="90" spans="59:59">
+      <c r="BG90" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="93" spans="58:58">
-      <c r="BF93" t="s">
+    <row r="91" spans="59:59">
+      <c r="BG91" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="94" spans="58:58">
-      <c r="BF94" t="s">
+    <row r="92" spans="59:59">
+      <c r="BG92" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="95" spans="58:58">
-      <c r="BF95" t="s">
+    <row r="93" spans="59:59">
+      <c r="BG93" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="96" spans="58:58">
-      <c r="BF96" t="s">
+    <row r="94" spans="59:59">
+      <c r="BG94" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="97" spans="58:58">
-      <c r="BF97" t="s">
+    <row r="95" spans="59:59">
+      <c r="BG95" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="98" spans="58:58">
-      <c r="BF98" t="s">
+    <row r="96" spans="59:59">
+      <c r="BG96" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="99" spans="58:58">
-      <c r="BF99" t="s">
+    <row r="97" spans="59:59">
+      <c r="BG97" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="100" spans="58:58">
-      <c r="BF100" t="s">
+    <row r="98" spans="59:59">
+      <c r="BG98" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="101" spans="58:58">
-      <c r="BF101" t="s">
+    <row r="99" spans="59:59">
+      <c r="BG99" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="102" spans="58:58">
-      <c r="BF102" t="s">
+    <row r="100" spans="59:59">
+      <c r="BG100" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="103" spans="58:58">
-      <c r="BF103" t="s">
+    <row r="101" spans="59:59">
+      <c r="BG101" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="104" spans="58:58">
-      <c r="BF104" t="s">
+    <row r="102" spans="59:59">
+      <c r="BG102" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="105" spans="58:58">
-      <c r="BF105" t="s">
+    <row r="103" spans="59:59">
+      <c r="BG103" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="106" spans="58:58">
-      <c r="BF106" t="s">
+    <row r="104" spans="59:59">
+      <c r="BG104" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="107" spans="58:58">
-      <c r="BF107" t="s">
+    <row r="105" spans="59:59">
+      <c r="BG105" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="108" spans="58:58">
-      <c r="BF108" t="s">
+    <row r="106" spans="59:59">
+      <c r="BG106" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="109" spans="58:58">
-      <c r="BF109" t="s">
+    <row r="107" spans="59:59">
+      <c r="BG107" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="110" spans="58:58">
-      <c r="BF110" t="s">
+    <row r="108" spans="59:59">
+      <c r="BG108" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="111" spans="58:58">
-      <c r="BF111" t="s">
+    <row r="109" spans="59:59">
+      <c r="BG109" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="112" spans="58:58">
-      <c r="BF112" t="s">
+    <row r="110" spans="59:59">
+      <c r="BG110" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="113" spans="58:58">
-      <c r="BF113" t="s">
+    <row r="111" spans="59:59">
+      <c r="BG111" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="114" spans="58:58">
-      <c r="BF114" t="s">
+    <row r="112" spans="59:59">
+      <c r="BG112" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="115" spans="58:58">
-      <c r="BF115" t="s">
+    <row r="113" spans="59:59">
+      <c r="BG113" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="116" spans="58:58">
-      <c r="BF116" t="s">
+    <row r="114" spans="59:59">
+      <c r="BG114" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="117" spans="58:58">
-      <c r="BF117" t="s">
+    <row r="115" spans="59:59">
+      <c r="BG115" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="118" spans="58:58">
-      <c r="BF118" t="s">
+    <row r="116" spans="59:59">
+      <c r="BG116" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="119" spans="58:58">
-      <c r="BF119" t="s">
+    <row r="117" spans="59:59">
+      <c r="BG117" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="120" spans="58:58">
-      <c r="BF120" t="s">
+    <row r="118" spans="59:59">
+      <c r="BG118" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="58:58">
-      <c r="BF121" t="s">
+    <row r="119" spans="59:59">
+      <c r="BG119" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="122" spans="58:58">
-      <c r="BF122" t="s">
+    <row r="120" spans="59:59">
+      <c r="BG120" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="123" spans="58:58">
-      <c r="BF123" t="s">
+    <row r="121" spans="59:59">
+      <c r="BG121" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="124" spans="58:58">
-      <c r="BF124" t="s">
+    <row r="122" spans="59:59">
+      <c r="BG122" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="125" spans="58:58">
-      <c r="BF125" t="s">
+    <row r="123" spans="59:59">
+      <c r="BG123" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="126" spans="58:58">
-      <c r="BF126" t="s">
+    <row r="124" spans="59:59">
+      <c r="BG124" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="127" spans="58:58">
-      <c r="BF127" t="s">
+    <row r="125" spans="59:59">
+      <c r="BG125" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="128" spans="58:58">
-      <c r="BF128" t="s">
+    <row r="126" spans="59:59">
+      <c r="BG126" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="129" spans="58:58">
-      <c r="BF129" t="s">
+    <row r="127" spans="59:59">
+      <c r="BG127" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="130" spans="58:58">
-      <c r="BF130" t="s">
+    <row r="128" spans="59:59">
+      <c r="BG128" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="131" spans="58:58">
-      <c r="BF131" t="s">
+    <row r="129" spans="59:59">
+      <c r="BG129" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="132" spans="58:58">
-      <c r="BF132" t="s">
+    <row r="130" spans="59:59">
+      <c r="BG130" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="133" spans="58:58">
-      <c r="BF133" t="s">
+    <row r="131" spans="59:59">
+      <c r="BG131" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="134" spans="58:58">
-      <c r="BF134" t="s">
+    <row r="132" spans="59:59">
+      <c r="BG132" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="135" spans="58:58">
-      <c r="BF135" t="s">
+    <row r="133" spans="59:59">
+      <c r="BG133" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="136" spans="58:58">
-      <c r="BF136" t="s">
+    <row r="134" spans="59:59">
+      <c r="BG134" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="137" spans="58:58">
-      <c r="BF137" t="s">
+    <row r="135" spans="59:59">
+      <c r="BG135" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="138" spans="58:58">
-      <c r="BF138" t="s">
+    <row r="136" spans="59:59">
+      <c r="BG136" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="139" spans="58:58">
-      <c r="BF139" t="s">
+    <row r="137" spans="59:59">
+      <c r="BG137" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="140" spans="58:58">
-      <c r="BF140" t="s">
+    <row r="138" spans="59:59">
+      <c r="BG138" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="141" spans="58:58">
-      <c r="BF141" t="s">
+    <row r="139" spans="59:59">
+      <c r="BG139" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="142" spans="58:58">
-      <c r="BF142" t="s">
+    <row r="140" spans="59:59">
+      <c r="BG140" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="143" spans="58:58">
-      <c r="BF143" t="s">
+    <row r="141" spans="59:59">
+      <c r="BG141" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="144" spans="58:58">
-      <c r="BF144" t="s">
+    <row r="142" spans="59:59">
+      <c r="BG142" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="145" spans="58:58">
-      <c r="BF145" t="s">
+    <row r="143" spans="59:59">
+      <c r="BG143" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="146" spans="58:58">
-      <c r="BF146" t="s">
+    <row r="144" spans="59:59">
+      <c r="BG144" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="147" spans="58:58">
-      <c r="BF147" t="s">
+    <row r="145" spans="59:59">
+      <c r="BG145" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="148" spans="58:58">
-      <c r="BF148" t="s">
+    <row r="146" spans="59:59">
+      <c r="BG146" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="149" spans="58:58">
-      <c r="BF149" t="s">
+    <row r="147" spans="59:59">
+      <c r="BG147" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="150" spans="58:58">
-      <c r="BF150" t="s">
+    <row r="148" spans="59:59">
+      <c r="BG148" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="151" spans="58:58">
-      <c r="BF151" t="s">
+    <row r="149" spans="59:59">
+      <c r="BG149" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="152" spans="58:58">
-      <c r="BF152" t="s">
+    <row r="150" spans="59:59">
+      <c r="BG150" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="153" spans="58:58">
-      <c r="BF153" t="s">
+    <row r="151" spans="59:59">
+      <c r="BG151" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="154" spans="58:58">
-      <c r="BF154" t="s">
+    <row r="152" spans="59:59">
+      <c r="BG152" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="155" spans="58:58">
-      <c r="BF155" t="s">
+    <row r="153" spans="59:59">
+      <c r="BG153" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="156" spans="58:58">
-      <c r="BF156" t="s">
+    <row r="154" spans="59:59">
+      <c r="BG154" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="157" spans="58:58">
-      <c r="BF157" t="s">
+    <row r="155" spans="59:59">
+      <c r="BG155" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="158" spans="58:58">
-      <c r="BF158" t="s">
+    <row r="156" spans="59:59">
+      <c r="BG156" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="159" spans="58:58">
-      <c r="BF159" t="s">
+    <row r="157" spans="59:59">
+      <c r="BG157" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="160" spans="58:58">
-      <c r="BF160" t="s">
+    <row r="158" spans="59:59">
+      <c r="BG158" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="161" spans="58:58">
-      <c r="BF161" t="s">
+    <row r="159" spans="59:59">
+      <c r="BG159" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="162" spans="58:58">
-      <c r="BF162" t="s">
+    <row r="160" spans="59:59">
+      <c r="BG160" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="163" spans="58:58">
-      <c r="BF163" t="s">
+    <row r="161" spans="59:59">
+      <c r="BG161" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="164" spans="58:58">
-      <c r="BF164" t="s">
+    <row r="162" spans="59:59">
+      <c r="BG162" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="165" spans="58:58">
-      <c r="BF165" t="s">
+    <row r="163" spans="59:59">
+      <c r="BG163" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="166" spans="58:58">
-      <c r="BF166" t="s">
+    <row r="164" spans="59:59">
+      <c r="BG164" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="167" spans="58:58">
-      <c r="BF167" t="s">
+    <row r="165" spans="59:59">
+      <c r="BG165" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="168" spans="58:58">
-      <c r="BF168" t="s">
+    <row r="166" spans="59:59">
+      <c r="BG166" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="169" spans="58:58">
-      <c r="BF169" t="s">
+    <row r="167" spans="59:59">
+      <c r="BG167" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="170" spans="58:58">
-      <c r="BF170" t="s">
+    <row r="168" spans="59:59">
+      <c r="BG168" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="171" spans="58:58">
-      <c r="BF171" t="s">
+    <row r="169" spans="59:59">
+      <c r="BG169" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="172" spans="58:58">
-      <c r="BF172" t="s">
+    <row r="170" spans="59:59">
+      <c r="BG170" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="173" spans="58:58">
-      <c r="BF173" t="s">
+    <row r="171" spans="59:59">
+      <c r="BG171" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="174" spans="58:58">
-      <c r="BF174" t="s">
+    <row r="172" spans="59:59">
+      <c r="BG172" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="175" spans="58:58">
-      <c r="BF175" t="s">
+    <row r="173" spans="59:59">
+      <c r="BG173" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="176" spans="58:58">
-      <c r="BF176" t="s">
+    <row r="174" spans="59:59">
+      <c r="BG174" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="177" spans="58:58">
-      <c r="BF177" t="s">
+    <row r="175" spans="59:59">
+      <c r="BG175" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="178" spans="58:58">
-      <c r="BF178" t="s">
+    <row r="176" spans="59:59">
+      <c r="BG176" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="179" spans="58:58">
-      <c r="BF179" t="s">
+    <row r="177" spans="59:59">
+      <c r="BG177" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="180" spans="58:58">
-      <c r="BF180" t="s">
+    <row r="178" spans="59:59">
+      <c r="BG178" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="181" spans="58:58">
-      <c r="BF181" t="s">
+    <row r="179" spans="59:59">
+      <c r="BG179" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="182" spans="58:58">
-      <c r="BF182" t="s">
+    <row r="180" spans="59:59">
+      <c r="BG180" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="183" spans="58:58">
-      <c r="BF183" t="s">
+    <row r="181" spans="59:59">
+      <c r="BG181" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="184" spans="58:58">
-      <c r="BF184" t="s">
+    <row r="182" spans="59:59">
+      <c r="BG182" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="185" spans="58:58">
-      <c r="BF185" t="s">
+    <row r="183" spans="59:59">
+      <c r="BG183" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="186" spans="58:58">
-      <c r="BF186" t="s">
+    <row r="184" spans="59:59">
+      <c r="BG184" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="187" spans="58:58">
-      <c r="BF187" t="s">
+    <row r="185" spans="59:59">
+      <c r="BG185" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="188" spans="58:58">
-      <c r="BF188" t="s">
+    <row r="186" spans="59:59">
+      <c r="BG186" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="189" spans="58:58">
-      <c r="BF189" t="s">
+    <row r="187" spans="59:59">
+      <c r="BG187" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="190" spans="58:58">
-      <c r="BF190" t="s">
+    <row r="188" spans="59:59">
+      <c r="BG188" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="191" spans="58:58">
-      <c r="BF191" t="s">
+    <row r="189" spans="59:59">
+      <c r="BG189" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="192" spans="58:58">
-      <c r="BF192" t="s">
+    <row r="190" spans="59:59">
+      <c r="BG190" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="193" spans="58:58">
-      <c r="BF193" t="s">
+    <row r="191" spans="59:59">
+      <c r="BG191" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="194" spans="58:58">
-      <c r="BF194" t="s">
+    <row r="192" spans="59:59">
+      <c r="BG192" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="195" spans="58:58">
-      <c r="BF195" t="s">
+    <row r="193" spans="59:59">
+      <c r="BG193" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="196" spans="58:58">
-      <c r="BF196" t="s">
+    <row r="194" spans="59:59">
+      <c r="BG194" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="197" spans="58:58">
-      <c r="BF197" t="s">
+    <row r="195" spans="59:59">
+      <c r="BG195" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="198" spans="58:58">
-      <c r="BF198" t="s">
+    <row r="196" spans="59:59">
+      <c r="BG196" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="199" spans="58:58">
-      <c r="BF199" t="s">
+    <row r="197" spans="59:59">
+      <c r="BG197" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="200" spans="58:58">
-      <c r="BF200" t="s">
+    <row r="198" spans="59:59">
+      <c r="BG198" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="201" spans="58:58">
-      <c r="BF201" t="s">
+    <row r="199" spans="59:59">
+      <c r="BG199" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="202" spans="58:58">
-      <c r="BF202" t="s">
+    <row r="200" spans="59:59">
+      <c r="BG200" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="203" spans="58:58">
-      <c r="BF203" t="s">
+    <row r="201" spans="59:59">
+      <c r="BG201" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="204" spans="58:58">
-      <c r="BF204" t="s">
+    <row r="202" spans="59:59">
+      <c r="BG202" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="205" spans="58:58">
-      <c r="BF205" t="s">
+    <row r="203" spans="59:59">
+      <c r="BG203" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="206" spans="58:58">
-      <c r="BF206" t="s">
+    <row r="204" spans="59:59">
+      <c r="BG204" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="207" spans="58:58">
-      <c r="BF207" t="s">
+    <row r="205" spans="59:59">
+      <c r="BG205" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="208" spans="58:58">
-      <c r="BF208" t="s">
+    <row r="206" spans="59:59">
+      <c r="BG206" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="209" spans="58:58">
-      <c r="BF209" t="s">
+    <row r="207" spans="59:59">
+      <c r="BG207" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="210" spans="58:58">
-      <c r="BF210" t="s">
+    <row r="208" spans="59:59">
+      <c r="BG208" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="211" spans="58:58">
-      <c r="BF211" t="s">
+    <row r="209" spans="59:59">
+      <c r="BG209" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="212" spans="58:58">
-      <c r="BF212" t="s">
+    <row r="210" spans="59:59">
+      <c r="BG210" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="213" spans="58:58">
-      <c r="BF213" t="s">
+    <row r="211" spans="59:59">
+      <c r="BG211" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="214" spans="58:58">
-      <c r="BF214" t="s">
+    <row r="212" spans="59:59">
+      <c r="BG212" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="215" spans="58:58">
-      <c r="BF215" t="s">
+    <row r="213" spans="59:59">
+      <c r="BG213" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="216" spans="58:58">
-      <c r="BF216" t="s">
+    <row r="214" spans="59:59">
+      <c r="BG214" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="217" spans="58:58">
-      <c r="BF217" t="s">
+    <row r="215" spans="59:59">
+      <c r="BG215" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="218" spans="58:58">
-      <c r="BF218" t="s">
+    <row r="216" spans="59:59">
+      <c r="BG216" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="219" spans="58:58">
-      <c r="BF219" t="s">
+    <row r="217" spans="59:59">
+      <c r="BG217" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="220" spans="58:58">
-      <c r="BF220" t="s">
+    <row r="218" spans="59:59">
+      <c r="BG218" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="221" spans="58:58">
-      <c r="BF221" t="s">
+    <row r="219" spans="59:59">
+      <c r="BG219" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="222" spans="58:58">
-      <c r="BF222" t="s">
+    <row r="220" spans="59:59">
+      <c r="BG220" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="223" spans="58:58">
-      <c r="BF223" t="s">
+    <row r="221" spans="59:59">
+      <c r="BG221" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="224" spans="58:58">
-      <c r="BF224" t="s">
+    <row r="222" spans="59:59">
+      <c r="BG222" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="225" spans="58:58">
-      <c r="BF225" t="s">
+    <row r="223" spans="59:59">
+      <c r="BG223" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="226" spans="58:58">
-      <c r="BF226" t="s">
+    <row r="224" spans="59:59">
+      <c r="BG224" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="227" spans="58:58">
-      <c r="BF227" t="s">
+    <row r="225" spans="59:59">
+      <c r="BG225" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="228" spans="58:58">
-      <c r="BF228" t="s">
+    <row r="226" spans="59:59">
+      <c r="BG226" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="229" spans="58:58">
-      <c r="BF229" t="s">
+    <row r="227" spans="59:59">
+      <c r="BG227" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="230" spans="58:58">
-      <c r="BF230" t="s">
+    <row r="228" spans="59:59">
+      <c r="BG228" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="231" spans="58:58">
-      <c r="BF231" t="s">
+    <row r="229" spans="59:59">
+      <c r="BG229" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="232" spans="58:58">
-      <c r="BF232" t="s">
+    <row r="230" spans="59:59">
+      <c r="BG230" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="233" spans="58:58">
-      <c r="BF233" t="s">
+    <row r="231" spans="59:59">
+      <c r="BG231" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="234" spans="58:58">
-      <c r="BF234" t="s">
+    <row r="232" spans="59:59">
+      <c r="BG232" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="235" spans="58:58">
-      <c r="BF235" t="s">
+    <row r="233" spans="59:59">
+      <c r="BG233" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="236" spans="58:58">
-      <c r="BF236" t="s">
+    <row r="234" spans="59:59">
+      <c r="BG234" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="237" spans="58:58">
-      <c r="BF237" t="s">
+    <row r="235" spans="59:59">
+      <c r="BG235" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="238" spans="58:58">
-      <c r="BF238" t="s">
+    <row r="236" spans="59:59">
+      <c r="BG236" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="239" spans="58:58">
-      <c r="BF239" t="s">
+    <row r="237" spans="59:59">
+      <c r="BG237" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="240" spans="58:58">
-      <c r="BF240" t="s">
+    <row r="238" spans="59:59">
+      <c r="BG238" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="241" spans="58:58">
-      <c r="BF241" t="s">
+    <row r="239" spans="59:59">
+      <c r="BG239" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="242" spans="58:58">
-      <c r="BF242" t="s">
+    <row r="240" spans="59:59">
+      <c r="BG240" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="243" spans="58:58">
-      <c r="BF243" t="s">
+    <row r="241" spans="59:59">
+      <c r="BG241" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="244" spans="58:58">
-      <c r="BF244" t="s">
+    <row r="242" spans="59:59">
+      <c r="BG242" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="245" spans="58:58">
-      <c r="BF245" t="s">
+    <row r="243" spans="59:59">
+      <c r="BG243" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="246" spans="58:58">
-      <c r="BF246" t="s">
+    <row r="244" spans="59:59">
+      <c r="BG244" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="247" spans="58:58">
-      <c r="BF247" t="s">
+    <row r="245" spans="59:59">
+      <c r="BG245" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="248" spans="58:58">
-      <c r="BF248" t="s">
+    <row r="246" spans="59:59">
+      <c r="BG246" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="249" spans="58:58">
-      <c r="BF249" t="s">
+    <row r="247" spans="59:59">
+      <c r="BG247" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="250" spans="58:58">
-      <c r="BF250" t="s">
+    <row r="248" spans="59:59">
+      <c r="BG248" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="251" spans="58:58">
-      <c r="BF251" t="s">
+    <row r="249" spans="59:59">
+      <c r="BG249" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="252" spans="58:58">
-      <c r="BF252" t="s">
+    <row r="250" spans="59:59">
+      <c r="BG250" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="253" spans="58:58">
-      <c r="BF253" t="s">
+    <row r="251" spans="59:59">
+      <c r="BG251" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="254" spans="58:58">
-      <c r="BF254" t="s">
+    <row r="252" spans="59:59">
+      <c r="BG252" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="255" spans="58:58">
-      <c r="BF255" t="s">
+    <row r="253" spans="59:59">
+      <c r="BG253" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="256" spans="58:58">
-      <c r="BF256" t="s">
+    <row r="254" spans="59:59">
+      <c r="BG254" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="257" spans="58:58">
-      <c r="BF257" t="s">
+    <row r="255" spans="59:59">
+      <c r="BG255" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="258" spans="58:58">
-      <c r="BF258" t="s">
+    <row r="256" spans="59:59">
+      <c r="BG256" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="259" spans="58:58">
-      <c r="BF259" t="s">
+    <row r="257" spans="59:59">
+      <c r="BG257" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="260" spans="58:58">
-      <c r="BF260" t="s">
+    <row r="258" spans="59:59">
+      <c r="BG258" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="261" spans="58:58">
-      <c r="BF261" t="s">
+    <row r="259" spans="59:59">
+      <c r="BG259" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="262" spans="58:58">
-      <c r="BF262" t="s">
+    <row r="260" spans="59:59">
+      <c r="BG260" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="263" spans="58:58">
-      <c r="BF263" t="s">
+    <row r="261" spans="59:59">
+      <c r="BG261" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="264" spans="58:58">
-      <c r="BF264" t="s">
+    <row r="262" spans="59:59">
+      <c r="BG262" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="265" spans="58:58">
-      <c r="BF265" t="s">
+    <row r="263" spans="59:59">
+      <c r="BG263" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="266" spans="58:58">
-      <c r="BF266" t="s">
+    <row r="264" spans="59:59">
+      <c r="BG264" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="267" spans="58:58">
-      <c r="BF267" t="s">
+    <row r="265" spans="59:59">
+      <c r="BG265" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="268" spans="58:58">
-      <c r="BF268" t="s">
+    <row r="266" spans="59:59">
+      <c r="BG266" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="269" spans="58:58">
-      <c r="BF269" t="s">
+    <row r="267" spans="59:59">
+      <c r="BG267" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="270" spans="58:58">
-      <c r="BF270" t="s">
+    <row r="268" spans="59:59">
+      <c r="BG268" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="271" spans="58:58">
-      <c r="BF271" t="s">
+    <row r="269" spans="59:59">
+      <c r="BG269" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="272" spans="58:58">
-      <c r="BF272" t="s">
+    <row r="270" spans="59:59">
+      <c r="BG270" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="273" spans="58:58">
-      <c r="BF273" t="s">
+    <row r="271" spans="59:59">
+      <c r="BG271" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="274" spans="58:58">
-      <c r="BF274" t="s">
+    <row r="272" spans="59:59">
+      <c r="BG272" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="275" spans="58:58">
-      <c r="BF275" t="s">
+    <row r="273" spans="59:59">
+      <c r="BG273" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="276" spans="58:58">
-      <c r="BF276" t="s">
+    <row r="274" spans="59:59">
+      <c r="BG274" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="277" spans="58:58">
-      <c r="BF277" t="s">
+    <row r="275" spans="59:59">
+      <c r="BG275" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="278" spans="58:58">
-      <c r="BF278" t="s">
+    <row r="276" spans="59:59">
+      <c r="BG276" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="279" spans="58:58">
-      <c r="BF279" t="s">
+    <row r="277" spans="59:59">
+      <c r="BG277" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="280" spans="58:58">
-      <c r="BF280" t="s">
+    <row r="278" spans="59:59">
+      <c r="BG278" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="281" spans="58:58">
-      <c r="BF281" t="s">
+    <row r="279" spans="59:59">
+      <c r="BG279" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="282" spans="58:58">
-      <c r="BF282" t="s">
+    <row r="280" spans="59:59">
+      <c r="BG280" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="283" spans="58:58">
-      <c r="BF283" t="s">
+    <row r="281" spans="59:59">
+      <c r="BG281" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="284" spans="58:58">
-      <c r="BF284" t="s">
+    <row r="282" spans="59:59">
+      <c r="BG282" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="285" spans="58:58">
-      <c r="BF285" t="s">
+    <row r="283" spans="59:59">
+      <c r="BG283" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="286" spans="58:58">
-      <c r="BF286" t="s">
+    <row r="284" spans="59:59">
+      <c r="BG284" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="287" spans="58:58">
-      <c r="BF287" t="s">
+    <row r="285" spans="59:59">
+      <c r="BG285" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="288" spans="58:58">
-      <c r="BF288" t="s">
+    <row r="286" spans="59:59">
+      <c r="BG286" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="289" spans="58:58">
-      <c r="BF289" t="s">
+    <row r="287" spans="59:59">
+      <c r="BG287" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="290" spans="58:58">
-      <c r="BF290" t="s">
+    <row r="288" spans="59:59">
+      <c r="BG288" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="291" spans="58:58">
-      <c r="BF291" t="s">
+    <row r="289" spans="59:59">
+      <c r="BG289" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="292" spans="58:58">
-      <c r="BF292" t="s">
+    <row r="290" spans="59:59">
+      <c r="BG290" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="293" spans="58:58">
-      <c r="BF293" t="s">
+    <row r="291" spans="59:59">
+      <c r="BG291" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="294" spans="58:58">
-      <c r="BF294" t="s">
+    <row r="292" spans="59:59">
+      <c r="BG292" t="s">
         <v>720</v>
+      </c>
+    </row>
+    <row r="293" spans="59:59">
+      <c r="BG293" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="294" spans="59:59">
+      <c r="BG294" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$W$1:$W$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AH$1:$AH$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DU$1:$DU$4</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="918">
   <si>
     <t>alias</t>
   </si>
@@ -453,6 +453,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -543,6 +546,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1533,9 +1539,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1554,6 +1557,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1755,6 +1761,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1764,9 +1773,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1806,7 +1812,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1875,6 +1881,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1950,6 +1959,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1971,6 +1983,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2016,6 +2031,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2028,6 +2046,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2037,9 +2058,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2064,6 +2082,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2124,10 +2145,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3296,10 +3317,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3340,10 +3361,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3370,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3387,7 +3408,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3404,7 +3425,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3421,7 +3442,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3438,7 +3459,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3455,7 +3476,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3472,7 +3493,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3489,7 +3510,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3506,7 +3527,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3523,7 +3544,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3537,7 +3558,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3551,7 +3572,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3565,7 +3586,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3579,7 +3600,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3593,7 +3614,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3607,7 +3628,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3621,7 +3642,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3635,7 +3656,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3645,8 +3666,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3657,7 +3681,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3668,7 +3692,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3679,7 +3703,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3690,7 +3714,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3701,7 +3725,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3712,7 +3736,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3723,7 +3747,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3734,7 +3758,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3745,7 +3769,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3756,7 +3780,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3767,7 +3791,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3778,7 +3802,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3789,7 +3813,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3797,7 +3821,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3805,7 +3829,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3813,7 +3837,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3821,7 +3845,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3829,7 +3853,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3837,7 +3861,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3845,7 +3869,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3853,7 +3877,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3861,7 +3885,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3869,236 +3893,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4120,27 +4149,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4160,122 +4189,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4299,924 +4328,924 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:154" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -5252,1611 +5281,1636 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:DU289"/>
+  <dimension ref="H1:DU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:125">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AH1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BG1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="DU1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
     </row>
     <row r="2" spans="8:125">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="W2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AH2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BG2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="DU2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="3" spans="8:125">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AH3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="BG3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="DU3" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" spans="8:125">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BG4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DU4" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="8:125">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BG5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="8:125">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BG6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="8:125">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BG7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="8:125">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BG8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="8:125">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BG9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="8:125">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="BG10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="8:125">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="BG11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="8:125">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="BG12" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="8:125">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="BG13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="8:125">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="BG14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="8:125">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="BG15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="8:125">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="BG16" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="8:59">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="BG17" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" spans="8:59">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="BG18" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="8:59">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="BG19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="8:59">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="BG20" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="8:59">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="BG21" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="8:59">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="BG22" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="8:59">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="BG23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="8:59">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="BG24" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="8:59">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="BG25" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="8:59">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="BG26" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="8:59">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BG27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="8:59">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="BG28" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="8:59">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="BG29" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" spans="8:59">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="BG30" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="8:59">
       <c r="BG31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="32" spans="8:59">
       <c r="BG32" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="59:59">
       <c r="BG33" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34" spans="59:59">
       <c r="BG34" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35" spans="59:59">
       <c r="BG35" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="59:59">
       <c r="BG36" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="59:59">
       <c r="BG37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="59:59">
       <c r="BG38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" spans="59:59">
       <c r="BG39" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="59:59">
       <c r="BG40" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="59:59">
       <c r="BG41" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="42" spans="59:59">
       <c r="BG42" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="59:59">
       <c r="BG43" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="59:59">
       <c r="BG44" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" spans="59:59">
       <c r="BG45" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="59:59">
       <c r="BG46" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="59:59">
       <c r="BG47" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="59:59">
       <c r="BG48" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="59:59">
       <c r="BG49" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" spans="59:59">
       <c r="BG50" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51" spans="59:59">
       <c r="BG51" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" spans="59:59">
       <c r="BG52" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="59:59">
       <c r="BG53" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="54" spans="59:59">
       <c r="BG54" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="59:59">
       <c r="BG55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="59:59">
       <c r="BG56" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" spans="59:59">
       <c r="BG57" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="59:59">
       <c r="BG58" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="59" spans="59:59">
       <c r="BG59" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="60" spans="59:59">
       <c r="BG60" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" spans="59:59">
       <c r="BG61" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="62" spans="59:59">
       <c r="BG62" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="63" spans="59:59">
       <c r="BG63" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" spans="59:59">
       <c r="BG64" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="65" spans="59:59">
       <c r="BG65" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="66" spans="59:59">
       <c r="BG66" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="59:59">
       <c r="BG67" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="68" spans="59:59">
       <c r="BG68" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="59:59">
       <c r="BG69" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="59:59">
       <c r="BG70" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="59:59">
       <c r="BG71" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="59:59">
       <c r="BG72" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="59:59">
       <c r="BG73" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="59:59">
       <c r="BG74" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="59:59">
       <c r="BG75" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="59:59">
       <c r="BG76" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="59:59">
       <c r="BG77" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="59:59">
       <c r="BG78" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="79" spans="59:59">
       <c r="BG79" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="80" spans="59:59">
       <c r="BG80" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="81" spans="59:59">
       <c r="BG81" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="82" spans="59:59">
       <c r="BG82" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="83" spans="59:59">
       <c r="BG83" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" spans="59:59">
       <c r="BG84" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="85" spans="59:59">
       <c r="BG85" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="86" spans="59:59">
       <c r="BG86" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="87" spans="59:59">
       <c r="BG87" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="88" spans="59:59">
       <c r="BG88" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="89" spans="59:59">
       <c r="BG89" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" spans="59:59">
       <c r="BG90" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" spans="59:59">
       <c r="BG91" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="92" spans="59:59">
       <c r="BG92" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="93" spans="59:59">
       <c r="BG93" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="94" spans="59:59">
       <c r="BG94" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="95" spans="59:59">
       <c r="BG95" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="96" spans="59:59">
       <c r="BG96" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="97" spans="59:59">
       <c r="BG97" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="98" spans="59:59">
       <c r="BG98" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="99" spans="59:59">
       <c r="BG99" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100" spans="59:59">
       <c r="BG100" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="101" spans="59:59">
       <c r="BG101" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="102" spans="59:59">
       <c r="BG102" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="103" spans="59:59">
       <c r="BG103" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="104" spans="59:59">
       <c r="BG104" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="105" spans="59:59">
       <c r="BG105" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="106" spans="59:59">
       <c r="BG106" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="107" spans="59:59">
       <c r="BG107" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="108" spans="59:59">
       <c r="BG108" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="109" spans="59:59">
       <c r="BG109" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="110" spans="59:59">
       <c r="BG110" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="111" spans="59:59">
       <c r="BG111" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="112" spans="59:59">
       <c r="BG112" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113" spans="59:59">
       <c r="BG113" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" spans="59:59">
       <c r="BG114" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="115" spans="59:59">
       <c r="BG115" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="116" spans="59:59">
       <c r="BG116" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="117" spans="59:59">
       <c r="BG117" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="59:59">
       <c r="BG118" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="119" spans="59:59">
       <c r="BG119" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="120" spans="59:59">
       <c r="BG120" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="121" spans="59:59">
       <c r="BG121" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="59:59">
       <c r="BG122" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="123" spans="59:59">
       <c r="BG123" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124" spans="59:59">
       <c r="BG124" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="125" spans="59:59">
       <c r="BG125" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126" spans="59:59">
       <c r="BG126" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="127" spans="59:59">
       <c r="BG127" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="59:59">
       <c r="BG128" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="129" spans="59:59">
       <c r="BG129" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="130" spans="59:59">
       <c r="BG130" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="131" spans="59:59">
       <c r="BG131" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="132" spans="59:59">
       <c r="BG132" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="133" spans="59:59">
       <c r="BG133" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="134" spans="59:59">
       <c r="BG134" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135" spans="59:59">
       <c r="BG135" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="136" spans="59:59">
       <c r="BG136" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="137" spans="59:59">
       <c r="BG137" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="138" spans="59:59">
       <c r="BG138" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="139" spans="59:59">
       <c r="BG139" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="140" spans="59:59">
       <c r="BG140" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="141" spans="59:59">
       <c r="BG141" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="142" spans="59:59">
       <c r="BG142" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="143" spans="59:59">
       <c r="BG143" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="144" spans="59:59">
       <c r="BG144" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="145" spans="59:59">
       <c r="BG145" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="146" spans="59:59">
       <c r="BG146" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="147" spans="59:59">
       <c r="BG147" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="148" spans="59:59">
       <c r="BG148" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="149" spans="59:59">
       <c r="BG149" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="150" spans="59:59">
       <c r="BG150" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="151" spans="59:59">
       <c r="BG151" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="152" spans="59:59">
       <c r="BG152" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="59:59">
       <c r="BG153" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="154" spans="59:59">
       <c r="BG154" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="155" spans="59:59">
       <c r="BG155" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="156" spans="59:59">
       <c r="BG156" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="157" spans="59:59">
       <c r="BG157" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="158" spans="59:59">
       <c r="BG158" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="59:59">
       <c r="BG159" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="160" spans="59:59">
       <c r="BG160" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="161" spans="59:59">
       <c r="BG161" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="162" spans="59:59">
       <c r="BG162" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="163" spans="59:59">
       <c r="BG163" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="164" spans="59:59">
       <c r="BG164" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="165" spans="59:59">
       <c r="BG165" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="166" spans="59:59">
       <c r="BG166" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="167" spans="59:59">
       <c r="BG167" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="168" spans="59:59">
       <c r="BG168" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="169" spans="59:59">
       <c r="BG169" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="170" spans="59:59">
       <c r="BG170" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="171" spans="59:59">
       <c r="BG171" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="172" spans="59:59">
       <c r="BG172" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" spans="59:59">
       <c r="BG173" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" spans="59:59">
       <c r="BG174" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="175" spans="59:59">
       <c r="BG175" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="176" spans="59:59">
       <c r="BG176" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="177" spans="59:59">
       <c r="BG177" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="178" spans="59:59">
       <c r="BG178" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="179" spans="59:59">
       <c r="BG179" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="180" spans="59:59">
       <c r="BG180" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="181" spans="59:59">
       <c r="BG181" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="182" spans="59:59">
       <c r="BG182" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="183" spans="59:59">
       <c r="BG183" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="184" spans="59:59">
       <c r="BG184" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="185" spans="59:59">
       <c r="BG185" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="186" spans="59:59">
       <c r="BG186" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="59:59">
       <c r="BG187" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="188" spans="59:59">
       <c r="BG188" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="189" spans="59:59">
       <c r="BG189" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="190" spans="59:59">
       <c r="BG190" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="191" spans="59:59">
       <c r="BG191" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="192" spans="59:59">
       <c r="BG192" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="193" spans="59:59">
       <c r="BG193" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="194" spans="59:59">
       <c r="BG194" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="195" spans="59:59">
       <c r="BG195" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="196" spans="59:59">
       <c r="BG196" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="197" spans="59:59">
       <c r="BG197" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="198" spans="59:59">
       <c r="BG198" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="199" spans="59:59">
       <c r="BG199" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="200" spans="59:59">
       <c r="BG200" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="201" spans="59:59">
       <c r="BG201" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="202" spans="59:59">
       <c r="BG202" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="203" spans="59:59">
       <c r="BG203" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="204" spans="59:59">
       <c r="BG204" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="205" spans="59:59">
       <c r="BG205" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="206" spans="59:59">
       <c r="BG206" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="207" spans="59:59">
       <c r="BG207" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="208" spans="59:59">
       <c r="BG208" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="209" spans="59:59">
       <c r="BG209" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="210" spans="59:59">
       <c r="BG210" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="211" spans="59:59">
       <c r="BG211" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="212" spans="59:59">
       <c r="BG212" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="213" spans="59:59">
       <c r="BG213" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="214" spans="59:59">
       <c r="BG214" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="215" spans="59:59">
       <c r="BG215" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="216" spans="59:59">
       <c r="BG216" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="217" spans="59:59">
       <c r="BG217" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218" spans="59:59">
       <c r="BG218" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="219" spans="59:59">
       <c r="BG219" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="220" spans="59:59">
       <c r="BG220" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="221" spans="59:59">
       <c r="BG221" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="222" spans="59:59">
       <c r="BG222" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="223" spans="59:59">
       <c r="BG223" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="224" spans="59:59">
       <c r="BG224" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="225" spans="59:59">
       <c r="BG225" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="226" spans="59:59">
       <c r="BG226" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="227" spans="59:59">
       <c r="BG227" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="228" spans="59:59">
       <c r="BG228" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="229" spans="59:59">
       <c r="BG229" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="230" spans="59:59">
       <c r="BG230" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="231" spans="59:59">
       <c r="BG231" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="232" spans="59:59">
       <c r="BG232" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="233" spans="59:59">
       <c r="BG233" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="234" spans="59:59">
       <c r="BG234" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="235" spans="59:59">
       <c r="BG235" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="236" spans="59:59">
       <c r="BG236" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="237" spans="59:59">
       <c r="BG237" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="238" spans="59:59">
       <c r="BG238" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="239" spans="59:59">
       <c r="BG239" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="240" spans="59:59">
       <c r="BG240" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="241" spans="59:59">
       <c r="BG241" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="242" spans="59:59">
       <c r="BG242" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="243" spans="59:59">
       <c r="BG243" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="244" spans="59:59">
       <c r="BG244" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="245" spans="59:59">
       <c r="BG245" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="246" spans="59:59">
       <c r="BG246" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="247" spans="59:59">
       <c r="BG247" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="248" spans="59:59">
       <c r="BG248" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="249" spans="59:59">
       <c r="BG249" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="250" spans="59:59">
       <c r="BG250" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="251" spans="59:59">
       <c r="BG251" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="252" spans="59:59">
       <c r="BG252" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="253" spans="59:59">
       <c r="BG253" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="254" spans="59:59">
       <c r="BG254" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="255" spans="59:59">
       <c r="BG255" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="256" spans="59:59">
       <c r="BG256" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="257" spans="59:59">
       <c r="BG257" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="258" spans="59:59">
       <c r="BG258" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="259" spans="59:59">
       <c r="BG259" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="260" spans="59:59">
       <c r="BG260" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="261" spans="59:59">
       <c r="BG261" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="262" spans="59:59">
       <c r="BG262" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="263" spans="59:59">
       <c r="BG263" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="264" spans="59:59">
       <c r="BG264" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="265" spans="59:59">
       <c r="BG265" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="266" spans="59:59">
       <c r="BG266" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="267" spans="59:59">
       <c r="BG267" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="268" spans="59:59">
       <c r="BG268" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="269" spans="59:59">
       <c r="BG269" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="270" spans="59:59">
       <c r="BG270" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="271" spans="59:59">
       <c r="BG271" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="272" spans="59:59">
       <c r="BG272" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="273" spans="59:59">
       <c r="BG273" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="274" spans="59:59">
       <c r="BG274" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="275" spans="59:59">
       <c r="BG275" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="276" spans="59:59">
       <c r="BG276" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="277" spans="59:59">
       <c r="BG277" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="278" spans="59:59">
       <c r="BG278" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="279" spans="59:59">
       <c r="BG279" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="280" spans="59:59">
       <c r="BG280" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="281" spans="59:59">
       <c r="BG281" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="282" spans="59:59">
       <c r="BG282" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="283" spans="59:59">
       <c r="BG283" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="284" spans="59:59">
       <c r="BG284" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="285" spans="59:59">
       <c r="BG285" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="286" spans="59:59">
       <c r="BG286" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="287" spans="59:59">
       <c r="BG287" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="288" spans="59:59">
       <c r="BG288" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="289" spans="59:59">
       <c r="BG289" t="s">
-        <v>715</v>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="290" spans="59:59">
+      <c r="BG290" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="291" spans="59:59">
+      <c r="BG291" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="292" spans="59:59">
+      <c r="BG292" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="293" spans="59:59">
+      <c r="BG293" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="294" spans="59:59">
+      <c r="BG294" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -1032,7 +1032,7 @@
     <t>sample transport conditions</t>
   </si>
   <si>
-    <t>(Optional) Sample transport duration (in days or hrs) and temperature the sample was exposed to (e.g. 5.5 days; 20 °c) (Units: m2)</t>
+    <t>(Optional) Sample transport duration (in days or hrs) and temperature the sample was exposed to (e.g. 5.5 days; 20 °c) (Units: minute)</t>
   </si>
   <si>
     <t>sample collection device</t>
@@ -1209,19 +1209,19 @@
     <t>well identification number</t>
   </si>
   <si>
-    <t>(Optional) A unique identifier of a well or wellbore. this is part of the global framework for well identification initiative which is compiled by the professional petroleum data management association (ppdm) in an effort to improve well identification systems. (supporting information: https://ppdm.org/ and http://dl.ppdm.org/dl/690) (Units: year)</t>
+    <t>(Optional) A unique identifier of a well or wellbore. this is part of the global framework for well identification initiative which is compiled by the professional petroleum data management association (ppdm) in an effort to improve well identification systems. (supporting information: https://ppdm.org/ and http://dl.ppdm.org/dl/690)</t>
   </si>
   <si>
     <t>water cut</t>
   </si>
   <si>
-    <t>(Optional) Current amount of water (%) in a produced fluid stream; or the average of the combined streams (Units: year)</t>
+    <t>(Optional) Current amount of water (%) in a produced fluid stream; or the average of the combined streams (Units: %)</t>
   </si>
   <si>
     <t>production rate</t>
   </si>
   <si>
-    <t>(Optional) Oil and/or gas production rates per well (e.g. 524 m3 / day) (Units: °C)</t>
+    <t>(Optional) Oil and/or gas production rates per well (e.g. 524 m3 / day)</t>
   </si>
   <si>
     <t>field name</t>
@@ -1305,19 +1305,19 @@
     <t>organism count qpcr information</t>
   </si>
   <si>
-    <t>(Optional) If qpcr was used for the cell count, the target gene name, the primer sequence and the cycling conditions should also be provided. (example: 16s rrna; fwd:acgtagctatgacgt rev:gtgctagtcgagtac; initial denaturation:90c_5min; denaturation:90c_2min; annealing:52c_30 sec; elongation:72c_30 sec; 90 c for 1 min; final elongation:72c_5min; 30 cycles) (Units: year)</t>
+    <t>(Optional) If qpcr was used for the cell count, the target gene name, the primer sequence and the cycling conditions should also be provided. (example: 16s rrna; fwd:acgtagctatgacgt rev:gtgctagtcgagtac; initial denaturation:90c_5min; denaturation:90c_2min; annealing:52c_30 sec; elongation:72c_30 sec; 90 c for 1 min; final elongation:72c_5min; 30 cycles)</t>
   </si>
   <si>
     <t>hydrocarbon type produced</t>
   </si>
   <si>
-    <t>(Optional) Main hydrocarbon type produced from resource (i.e. oil, gas, condensate, etc). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Main hydrocarbon type produced from resource (i.e. oil, gas, condensate, etc). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>api gravity</t>
   </si>
   <si>
-    <t>(Optional) Api gravity is a measure of how heavy or light a petroleum liquid is compared to water (source: https://en.wikipedia.org/wiki/api_gravity) (e.g. 31.1api) (Units: °C)</t>
+    <t>(Optional) Api gravity is a measure of how heavy or light a petroleum liquid is compared to water (source: https://en.wikipedia.org/wiki/api_gravity) (e.g. 31.1api)</t>
   </si>
   <si>
     <t>sample storage duration</t>
@@ -2253,7 +2253,7 @@
     <t>permeability</t>
   </si>
   <si>
-    <t>(Optional) Measure of the ability of a hydrocarbon resource to allow fluids to pass through it. (additional information: https://en.wikipedia.org/wiki/permeability_(earth_sciences)) (Units: mm)</t>
+    <t>(Optional) Measure of the ability of a hydrocarbon resource to allow fluids to pass through it. (additional information: https://en.wikipedia.org/wiki/permeability_(earth_sciences))</t>
   </si>
   <si>
     <t>oil water contact depth</t>
@@ -2271,7 +2271,7 @@
     <t>source rock geological age</t>
   </si>
   <si>
-    <t>(Optional) Geological age of source rock (additional info: https://en.wikipedia.org/wiki/period_(geology)). if "other" is specified, please propose entry in "additional info" field (Units: °C)</t>
+    <t>(Optional) Geological age of source rock (additional info: https://en.wikipedia.org/wiki/period_(geology)). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>ammonium</t>
@@ -2445,7 +2445,7 @@
     <t>total acid number</t>
   </si>
   <si>
-    <t>(Optional) Total acid number(tan) is a measurement of acidity that is determined by the amount of potassium hydroxide in milligrams that is needed to neutralize the acids in one gram of oil. it is an important quality measurement of crude oil. (source: https://en.wikipedia.org/wiki/total_acid_number) (Units: year)</t>
+    <t>(Optional) Total acid number(tan) is a measurement of acidity that is determined by the amount of potassium hydroxide in milligrams that is needed to neutralize the acids in one gram of oil. it is an important quality measurement of crude oil. (source: https://en.wikipedia.org/wiki/total_acid_number)</t>
   </si>
   <si>
     <t>sulfate in formation water</t>
@@ -2457,7 +2457,7 @@
     <t>toluene</t>
   </si>
   <si>
-    <t>(Optional) Concentration of toluene in the sample (Units: year)</t>
+    <t>(Optional) Concentration of toluene in the sample</t>
   </si>
   <si>
     <t>asphaltenes wt%</t>
@@ -2469,7 +2469,7 @@
     <t>xylene</t>
   </si>
   <si>
-    <t>(Optional) Concentration of xylene in the sample (Units: m2)</t>
+    <t>(Optional) Concentration of xylene in the sample</t>
   </si>
   <si>
     <t>alkalinity method</t>
@@ -2481,7 +2481,7 @@
     <t>benzene</t>
   </si>
   <si>
-    <t>(Optional) Concentration of benzene in the sample (Units: m2)</t>
+    <t>(Optional) Concentration of benzene in the sample</t>
   </si>
   <si>
     <t>alkalinity</t>
@@ -2499,7 +2499,7 @@
     <t>source rock lithology</t>
   </si>
   <si>
-    <t>(Optional) Lithology of source rock (https://en.wikipedia.org/wiki/source_rock). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Lithology of source rock (https://en.wikipedia.org/wiki/source_rock). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>sample material type</t>
@@ -2529,13 +2529,13 @@
     <t>biocide administration</t>
   </si>
   <si>
-    <t>(Optional) List of biocides (commercial name of product and supplier) and date of administration (Units: year)</t>
+    <t>(Optional) List of biocides (commercial name of product and supplier) and date of administration</t>
   </si>
   <si>
     <t>chemical treatment method</t>
   </si>
   <si>
-    <t>(Optional) Method of chemical administration(dose, frequency, duration, time elapsed between administration and sampling) (e.g. 50 mg/l; twice a week; 1 hr; 0 days) (Units: J/K)</t>
+    <t>(Optional) Method of chemical administration(dose, frequency, duration, time elapsed between administration and sampling) (e.g. 50 mg/l; twice a week; 1 hr; 0 days)</t>
   </si>
   <si>
     <t>negative control type</t>
@@ -2595,7 +2595,7 @@
     <t>sample subtype</t>
   </si>
   <si>
-    <t>(Optional) Name of sample sub-type. for example if "sample type" is "produced water" then subtype could be "oil phase" or "water phase". if "other" is specified, please propose entry in "additional info" field (Units: m2)</t>
+    <t>(Optional) Name of sample sub-type. for example if "sample type" is "produced water" then subtype could be "oil phase" or "water phase". if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>preservative added to sample</t>
@@ -2697,7 +2697,7 @@
     <t>production start date</t>
   </si>
   <si>
-    <t>(Optional) Date of field's first production (Units: m)</t>
+    <t>(Optional) Date of field's first production</t>
   </si>
   <si>
     <t>aromatics wt%</t>
@@ -2724,7 +2724,7 @@
     <t>basin name</t>
   </si>
   <si>
-    <t>(Optional) Name of the basin (e.g. campos) (Units: g/m3)</t>
+    <t>(Optional) Name of the basin (e.g. campos)</t>
   </si>
   <si>
     <t>pour point</t>
@@ -2736,7 +2736,7 @@
     <t>reservoir name</t>
   </si>
   <si>
-    <t>(Optional) Name of the reservoir (e.g. carapebus) (Units: °C)</t>
+    <t>(Optional) Name of the reservoir (e.g. carapebus)</t>
   </si>
   <si>
     <t>hydrocarbon resource geological age</t>
@@ -2748,19 +2748,19 @@
     <t>depositional environment</t>
   </si>
   <si>
-    <t>(Optional) Main depositional environment (https://en.wikipedia.org/wiki/depositional_environment). if "other" is specified, please propose entry in "additional info" field (Units: m)</t>
+    <t>(Optional) Main depositional environment (https://en.wikipedia.org/wiki/depositional_environment). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>source rock kerogen type</t>
   </si>
   <si>
-    <t>(Optional) Origin of kerogen. type i: algal (aquatic), type ii: planktonic and soft plant material (aquatic or terrestrial), type iii: terrestrial woody/ fibrous plant material (terrestrial), type iv: oxidized recycled woody debris (terrestrial) (additional information: https://en.wikipedia.org/wiki/kerogen). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Origin of kerogen. type i: algal (aquatic), type ii: planktonic and soft plant material (aquatic or terrestrial), type iii: terrestrial woody/ fibrous plant material (terrestrial), type iv: oxidized recycled woody debris (terrestrial) (additional information: https://en.wikipedia.org/wiki/kerogen). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>hydrocarbon resource type</t>
   </si>
   <si>
-    <t>(Optional) Main hydrocarbon resource type. the term "hydrocarbon resource" hcr defined as a natural environmental feature containing large amounts of hydrocarbons at high concentrations potentially suitable for commercial exploitation. this term should not be confused with the hydrocarbon occurrence term which also includes hydrocarbon-rich environments with currently limited commercial interest such as seeps, outcrops, gas hydrates etc. if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Main hydrocarbon resource type. the term "hydrocarbon resource" hcr defined as a natural environmental feature containing large amounts of hydrocarbons at high concentrations potentially suitable for commercial exploitation. this term should not be confused with the hydrocarbon occurrence term which also includes hydrocarbon-rich environments with currently limited commercial interest such as seeps, outcrops, gas hydrates etc. if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>water production rate</t>
@@ -2772,7 +2772,7 @@
     <t>lithology</t>
   </si>
   <si>
-    <t>(Optional) Hydrocarbon resource main lithology (additional information: http://petrowiki.org/lithology_and_rock_type_determination). if "other" is specified, please propose entry in "additional info" field (Units: year)</t>
+    <t>(Optional) Hydrocarbon resource main lithology (additional information: http://petrowiki.org/lithology_and_rock_type_determination). if "other" is specified, please propose entry in "additional info" field</t>
   </si>
   <si>
     <t>hydrocarbon resource original temperature</t>
@@ -2790,7 +2790,7 @@
     <t>injection water breakthrough date of specific well</t>
   </si>
   <si>
-    <t>(Optional) Injection water breakthrough date per well following a secondary and/or tertiary recovery (Units: %)</t>
+    <t>(Optional) Injection water breakthrough date per well following a secondary and/or tertiary recovery</t>
   </si>
 </sst>
 </file>
@@ -5200,7 +5200,7 @@
         <v>886</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="EJ2" s="2" t="s">
         <v>889</v>

--- a/templates/ERC000058/metadata_template_ERC000058.xlsx
+++ b/templates/ERC000058/metadata_template_ERC000058.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BG$1:$BG$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="919">
   <si>
     <t>alias</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3320,7 +3323,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3364,7 +3367,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3391,7 +3394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4128,6 +4131,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4149,27 +4157,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4189,122 +4197,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4328,924 +4336,924 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="2" spans="1:154" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -5286,1631 +5294,1631 @@
   <sheetData>
     <row r="1" spans="8:125">
       <c r="H1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="W1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AH1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="BG1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="DU1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" spans="8:125">
       <c r="H2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AH2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BG2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="DU2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="8:125">
       <c r="H3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AH3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="BG3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="DU3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4" spans="8:125">
       <c r="H4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="BG4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="DU4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="8:125">
       <c r="H5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BG5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="8:125">
       <c r="H6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="BG6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="8:125">
       <c r="H7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BG7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="8:125">
       <c r="H8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="BG8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="8:125">
       <c r="H9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="BG9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="8:125">
       <c r="H10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="BG10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="8:125">
       <c r="H11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="BG11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="8:125">
       <c r="H12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BG12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="8:125">
       <c r="H13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BG13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="8:125">
       <c r="H14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BG14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="8:125">
       <c r="H15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="8:125">
       <c r="H16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BG16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="8:59">
       <c r="H17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="8:59">
       <c r="H18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="BG18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="8:59">
       <c r="H19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="BG19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="8:59">
       <c r="H20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="BG20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="8:59">
       <c r="H21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="BG21" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="8:59">
       <c r="H22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="BG22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="8:59">
       <c r="H23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="BG23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="8:59">
       <c r="H24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BG24" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="8:59">
       <c r="H25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BG25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="8:59">
       <c r="H26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BG26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="8:59">
       <c r="H27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BG27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="8:59">
       <c r="H28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BG28" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="8:59">
       <c r="H29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BG29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="8:59">
       <c r="H30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BG30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="8:59">
       <c r="BG31" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="8:59">
       <c r="BG32" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="59:59">
       <c r="BG33" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="59:59">
       <c r="BG34" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="59:59">
       <c r="BG35" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="59:59">
       <c r="BG36" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="59:59">
       <c r="BG37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="59:59">
       <c r="BG38" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="59:59">
       <c r="BG39" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" spans="59:59">
       <c r="BG40" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41" spans="59:59">
       <c r="BG41" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" spans="59:59">
       <c r="BG42" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" spans="59:59">
       <c r="BG43" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="44" spans="59:59">
       <c r="BG44" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="45" spans="59:59">
       <c r="BG45" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46" spans="59:59">
       <c r="BG46" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" spans="59:59">
       <c r="BG47" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" spans="59:59">
       <c r="BG48" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="59:59">
       <c r="BG49" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" spans="59:59">
       <c r="BG50" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="59:59">
       <c r="BG51" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="59:59">
       <c r="BG52" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="59:59">
       <c r="BG53" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="59:59">
       <c r="BG54" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="55" spans="59:59">
       <c r="BG55" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="59:59">
       <c r="BG56" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="57" spans="59:59">
       <c r="BG57" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="58" spans="59:59">
       <c r="BG58" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="59" spans="59:59">
       <c r="BG59" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="60" spans="59:59">
       <c r="BG60" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" spans="59:59">
       <c r="BG61" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" spans="59:59">
       <c r="BG62" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" spans="59:59">
       <c r="BG63" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="59:59">
       <c r="BG64" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="59:59">
       <c r="BG65" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="66" spans="59:59">
       <c r="BG66" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="67" spans="59:59">
       <c r="BG67" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="68" spans="59:59">
       <c r="BG68" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="69" spans="59:59">
       <c r="BG69" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" spans="59:59">
       <c r="BG70" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="59:59">
       <c r="BG71" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="59:59">
       <c r="BG72" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="59:59">
       <c r="BG73" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="59:59">
       <c r="BG74" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="75" spans="59:59">
       <c r="BG75" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76" spans="59:59">
       <c r="BG76" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="59:59">
       <c r="BG77" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="59:59">
       <c r="BG78" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" spans="59:59">
       <c r="BG79" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="80" spans="59:59">
       <c r="BG80" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="81" spans="59:59">
       <c r="BG81" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="82" spans="59:59">
       <c r="BG82" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="83" spans="59:59">
       <c r="BG83" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="84" spans="59:59">
       <c r="BG84" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="85" spans="59:59">
       <c r="BG85" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="86" spans="59:59">
       <c r="BG86" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="87" spans="59:59">
       <c r="BG87" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="88" spans="59:59">
       <c r="BG88" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="89" spans="59:59">
       <c r="BG89" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="90" spans="59:59">
       <c r="BG90" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="91" spans="59:59">
       <c r="BG91" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="92" spans="59:59">
       <c r="BG92" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="93" spans="59:59">
       <c r="BG93" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94" spans="59:59">
       <c r="BG94" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="95" spans="59:59">
       <c r="BG95" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96" spans="59:59">
       <c r="BG96" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="97" spans="59:59">
       <c r="BG97" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="98" spans="59:59">
       <c r="BG98" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99" spans="59:59">
       <c r="BG99" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="59:59">
       <c r="BG100" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="101" spans="59:59">
       <c r="BG101" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="59:59">
       <c r="BG102" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="103" spans="59:59">
       <c r="BG103" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="104" spans="59:59">
       <c r="BG104" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="105" spans="59:59">
       <c r="BG105" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="59:59">
       <c r="BG106" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="107" spans="59:59">
       <c r="BG107" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="108" spans="59:59">
       <c r="BG108" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="109" spans="59:59">
       <c r="BG109" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="110" spans="59:59">
       <c r="BG110" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="111" spans="59:59">
       <c r="BG111" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="112" spans="59:59">
       <c r="BG112" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="113" spans="59:59">
       <c r="BG113" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="114" spans="59:59">
       <c r="BG114" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="115" spans="59:59">
       <c r="BG115" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="116" spans="59:59">
       <c r="BG116" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="117" spans="59:59">
       <c r="BG117" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="118" spans="59:59">
       <c r="BG118" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" spans="59:59">
       <c r="BG119" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" spans="59:59">
       <c r="BG120" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="121" spans="59:59">
       <c r="BG121" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="122" spans="59:59">
       <c r="BG122" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="59:59">
       <c r="BG123" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="124" spans="59:59">
       <c r="BG124" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125" spans="59:59">
       <c r="BG125" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="59:59">
       <c r="BG126" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="127" spans="59:59">
       <c r="BG127" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="128" spans="59:59">
       <c r="BG128" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="129" spans="59:59">
       <c r="BG129" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="130" spans="59:59">
       <c r="BG130" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="131" spans="59:59">
       <c r="BG131" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="132" spans="59:59">
       <c r="BG132" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="133" spans="59:59">
       <c r="BG133" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="134" spans="59:59">
       <c r="BG134" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="135" spans="59:59">
       <c r="BG135" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="136" spans="59:59">
       <c r="BG136" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="137" spans="59:59">
       <c r="BG137" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="138" spans="59:59">
       <c r="BG138" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="139" spans="59:59">
       <c r="BG139" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="140" spans="59:59">
       <c r="BG140" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="141" spans="59:59">
       <c r="BG141" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="142" spans="59:59">
       <c r="BG142" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="143" spans="59:59">
       <c r="BG143" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="144" spans="59:59">
       <c r="BG144" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="145" spans="59:59">
       <c r="BG145" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="146" spans="59:59">
       <c r="BG146" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="147" spans="59:59">
       <c r="BG147" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="148" spans="59:59">
       <c r="BG148" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="149" spans="59:59">
       <c r="BG149" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="150" spans="59:59">
       <c r="BG150" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="151" spans="59:59">
       <c r="BG151" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="152" spans="59:59">
       <c r="BG152" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="153" spans="59:59">
       <c r="BG153" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="154" spans="59:59">
       <c r="BG154" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="155" spans="59:59">
       <c r="BG155" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="156" spans="59:59">
       <c r="BG156" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="157" spans="59:59">
       <c r="BG157" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="158" spans="59:59">
       <c r="BG158" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="159" spans="59:59">
       <c r="BG159" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="160" spans="59:59">
       <c r="BG160" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="161" spans="59:59">
       <c r="BG161" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="162" spans="59:59">
       <c r="BG162" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="163" spans="59:59">
       <c r="BG163" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="164" spans="59:59">
       <c r="BG164" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="165" spans="59:59">
       <c r="BG165" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="166" spans="59:59">
       <c r="BG166" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="167" spans="59:59">
       <c r="BG167" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="168" spans="59:59">
       <c r="BG168" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="169" spans="59:59">
       <c r="BG169" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="170" spans="59:59">
       <c r="BG170" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="171" spans="59:59">
       <c r="BG171" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="172" spans="59:59">
       <c r="BG172" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="173" spans="59:59">
       <c r="BG173" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="174" spans="59:59">
       <c r="BG174" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="175" spans="59:59">
       <c r="BG175" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="176" spans="59:59">
       <c r="BG176" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="177" spans="59:59">
       <c r="BG177" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="178" spans="59:59">
       <c r="BG178" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="179" spans="59:59">
       <c r="BG179" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="180" spans="59:59">
       <c r="BG180" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="181" spans="59:59">
       <c r="BG181" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="182" spans="59:59">
       <c r="BG182" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="183" spans="59:59">
       <c r="BG183" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="184" spans="59:59">
       <c r="BG184" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="185" spans="59:59">
       <c r="BG185" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="186" spans="59:59">
       <c r="BG186" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="187" spans="59:59">
       <c r="BG187" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="188" spans="59:59">
       <c r="BG188" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="189" spans="59:59">
       <c r="BG189" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="190" spans="59:59">
       <c r="BG190" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="191" spans="59:59">
       <c r="BG191" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="192" spans="59:59">
       <c r="BG192" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="193" spans="59:59">
       <c r="BG193" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="194" spans="59:59">
       <c r="BG194" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="195" spans="59:59">
       <c r="BG195" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="196" spans="59:59">
       <c r="BG196" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="197" spans="59:59">
       <c r="BG197" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="198" spans="59:59">
       <c r="BG198" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="199" spans="59:59">
       <c r="BG199" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="200" spans="59:59">
       <c r="BG200" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="201" spans="59:59">
       <c r="BG201" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="202" spans="59:59">
       <c r="BG202" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="203" spans="59:59">
       <c r="BG203" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="204" spans="59:59">
       <c r="BG204" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="205" spans="59:59">
       <c r="BG205" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="206" spans="59:59">
       <c r="BG206" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="207" spans="59:59">
       <c r="BG207" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="208" spans="59:59">
       <c r="BG208" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="209" spans="59:59">
       <c r="BG209" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="210" spans="59:59">
       <c r="BG210" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="211" spans="59:59">
       <c r="BG211" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="212" spans="59:59">
       <c r="BG212" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="213" spans="59:59">
       <c r="BG213" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="214" spans="59:59">
       <c r="BG214" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="215" spans="59:59">
       <c r="BG215" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="216" spans="59:59">
       <c r="BG216" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="217" spans="59:59">
       <c r="BG217" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="218" spans="59:59">
       <c r="BG218" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="219" spans="59:59">
       <c r="BG219" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="220" spans="59:59">
       <c r="BG220" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="221" spans="59:59">
       <c r="BG221" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="222" spans="59:59">
       <c r="BG222" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="223" spans="59:59">
       <c r="BG223" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="224" spans="59:59">
       <c r="BG224" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="225" spans="59:59">
       <c r="BG225" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="226" spans="59:59">
       <c r="BG226" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="227" spans="59:59">
       <c r="BG227" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="228" spans="59:59">
       <c r="BG228" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="229" spans="59:59">
       <c r="BG229" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="230" spans="59:59">
       <c r="BG230" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="231" spans="59:59">
       <c r="BG231" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="232" spans="59:59">
       <c r="BG232" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="233" spans="59:59">
       <c r="BG233" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="234" spans="59:59">
       <c r="BG234" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="235" spans="59:59">
       <c r="BG235" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="236" spans="59:59">
       <c r="BG236" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="237" spans="59:59">
       <c r="BG237" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="238" spans="59:59">
       <c r="BG238" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="239" spans="59:59">
       <c r="BG239" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="240" spans="59:59">
       <c r="BG240" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="241" spans="59:59">
       <c r="BG241" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="242" spans="59:59">
       <c r="BG242" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="243" spans="59:59">
       <c r="BG243" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="244" spans="59:59">
       <c r="BG244" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="245" spans="59:59">
       <c r="BG245" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="246" spans="59:59">
       <c r="BG246" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="247" spans="59:59">
       <c r="BG247" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="248" spans="59:59">
       <c r="BG248" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="249" spans="59:59">
       <c r="BG249" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="250" spans="59:59">
       <c r="BG250" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="251" spans="59:59">
       <c r="BG251" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="252" spans="59:59">
       <c r="BG252" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="253" spans="59:59">
       <c r="BG253" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="254" spans="59:59">
       <c r="BG254" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="255" spans="59:59">
       <c r="BG255" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="256" spans="59:59">
       <c r="BG256" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="257" spans="59:59">
       <c r="BG257" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="258" spans="59:59">
       <c r="BG258" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="259" spans="59:59">
       <c r="BG259" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="260" spans="59:59">
       <c r="BG260" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="261" spans="59:59">
       <c r="BG261" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="262" spans="59:59">
       <c r="BG262" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="263" spans="59:59">
       <c r="BG263" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="264" spans="59:59">
       <c r="BG264" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="265" spans="59:59">
       <c r="BG265" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="266" spans="59:59">
       <c r="BG266" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="267" spans="59:59">
       <c r="BG267" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="268" spans="59:59">
       <c r="BG268" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="269" spans="59:59">
       <c r="BG269" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="270" spans="59:59">
       <c r="BG270" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="271" spans="59:59">
       <c r="BG271" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="272" spans="59:59">
       <c r="BG272" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="273" spans="59:59">
       <c r="BG273" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="274" spans="59:59">
       <c r="BG274" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="275" spans="59:59">
       <c r="BG275" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="276" spans="59:59">
       <c r="BG276" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="277" spans="59:59">
       <c r="BG277" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="278" spans="59:59">
       <c r="BG278" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="279" spans="59:59">
       <c r="BG279" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="280" spans="59:59">
       <c r="BG280" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="281" spans="59:59">
       <c r="BG281" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="282" spans="59:59">
       <c r="BG282" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="283" spans="59:59">
       <c r="BG283" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="284" spans="59:59">
       <c r="BG284" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="285" spans="59:59">
       <c r="BG285" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="286" spans="59:59">
       <c r="BG286" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="287" spans="59:59">
       <c r="BG287" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="288" spans="59:59">
       <c r="BG288" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="289" spans="59:59">
       <c r="BG289" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="290" spans="59:59">
       <c r="BG290" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="291" spans="59:59">
       <c r="BG291" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="292" spans="59:59">
       <c r="BG292" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="293" spans="59:59">
       <c r="BG293" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="294" spans="59:59">
       <c r="BG294" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
